--- a/index.xlsx
+++ b/index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\OneDrive\문서\ALDrive\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C73C122-4DB1-4F21-B599-DB2063048229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E375CC-7D63-4D96-AF17-9D3E7999311A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
+    <workbookView xWindow="4545" yWindow="975" windowWidth="22725" windowHeight="13245" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -392,6 +392,22 @@
   </si>
   <si>
     <t>강기서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김태균</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오준환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고광윤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노승관</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1238,7 +1254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1402,8 +1418,29 @@
     <xf numFmtId="176" fontId="7" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1417,47 +1454,29 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1819,45 +1838,45 @@
   <sheetData>
     <row r="1" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="65"/>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
       <c r="U2" s="49"/>
     </row>
     <row r="3" spans="2:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:25" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="68"/>
+      <c r="R4" s="68"/>
+      <c r="S4" s="68"/>
     </row>
     <row r="5" spans="2:25" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:25" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1885,12 +1904,12 @@
       <c r="J6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="56" t="s">
+      <c r="L6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="58"/>
+      <c r="M6" s="64"/>
+      <c r="N6" s="64"/>
+      <c r="O6" s="65"/>
       <c r="T6"/>
       <c r="Y6"/>
     </row>
@@ -1898,7 +1917,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="66" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -1910,7 +1929,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="59">
+      <c r="H7" s="66">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -1938,7 +1957,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="59"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -1948,7 +1967,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="59"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -1974,7 +1993,7 @@
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="60"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -1984,7 +2003,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="59"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2002,7 +2021,7 @@
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="61"/>
+      <c r="C10" s="60"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2012,7 +2031,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="59"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2030,7 +2049,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="62">
+      <c r="C11" s="55">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2042,7 +2061,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="59"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2065,7 +2084,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="63"/>
+      <c r="C12" s="56"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2075,7 +2094,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="61"/>
+      <c r="H12" s="60"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2089,7 +2108,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="63"/>
+      <c r="C13" s="56"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2099,7 +2118,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="62">
+      <c r="H13" s="55">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2108,10 +2127,10 @@
       <c r="J13" s="32">
         <v>5</v>
       </c>
-      <c r="L13" s="67" t="s">
+      <c r="L13" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="68"/>
+      <c r="M13" s="70"/>
       <c r="N13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2125,7 +2144,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="63"/>
+      <c r="C14" s="56"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2135,7 +2154,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="63"/>
+      <c r="H14" s="56"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2143,13 +2162,13 @@
         <v>5</v>
       </c>
       <c r="K14" s="51"/>
-      <c r="L14" s="69" t="s">
+      <c r="L14" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="M14" s="70"/>
+      <c r="M14" s="72"/>
       <c r="N14" s="25">
         <f>E44+J44</f>
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="O14" s="15"/>
       <c r="T14"/>
@@ -2159,7 +2178,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="63"/>
+      <c r="C15" s="56"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2169,17 +2188,17 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="64"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J15" s="32">
         <v>5</v>
       </c>
-      <c r="L15" s="69" t="s">
+      <c r="L15" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="70"/>
+      <c r="M15" s="72"/>
       <c r="N15" s="26">
         <f>N11</f>
         <v>1000</v>
@@ -2192,7 +2211,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="64"/>
+      <c r="C16" s="57"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2202,7 +2221,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="62">
+      <c r="H16" s="55">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2211,13 +2230,13 @@
       <c r="J16" s="32">
         <v>5</v>
       </c>
-      <c r="L16" s="72" t="s">
+      <c r="L16" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="73"/>
+      <c r="M16" s="62"/>
       <c r="N16" s="27">
         <f>SUM(N14:N15)</f>
-        <v>1322</v>
+        <v>1342</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>70</v>
@@ -2229,7 +2248,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="62">
+      <c r="C17" s="55">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2241,7 +2260,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="63"/>
+      <c r="H17" s="56"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2255,7 +2274,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="63"/>
+      <c r="C18" s="56"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2265,7 +2284,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="64"/>
+      <c r="H18" s="57"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2280,7 +2299,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="63"/>
+      <c r="C19" s="56"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2290,7 +2309,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="62">
+      <c r="H19" s="55">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2306,7 +2325,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="63"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2316,7 +2335,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="63"/>
+      <c r="H20" s="56"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2330,7 +2349,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="64"/>
+      <c r="C21" s="57"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2340,7 +2359,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="64"/>
+      <c r="H21" s="57"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2354,7 +2373,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="62">
+      <c r="C22" s="55">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2382,7 +2401,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="63"/>
+      <c r="C23" s="56"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2409,7 +2428,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="63"/>
+      <c r="C24" s="56"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2435,7 +2454,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="63"/>
+      <c r="C25" s="56"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2461,7 +2480,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="63"/>
+      <c r="C26" s="56"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2471,7 +2490,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="55">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2487,7 +2506,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="64"/>
+      <c r="C27" s="57"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2497,7 +2516,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="63"/>
+      <c r="H27" s="56"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2539,7 +2558,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="71">
+      <c r="C29" s="58">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2567,7 +2586,7 @@
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="60"/>
+      <c r="C30" s="59"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2593,7 +2612,7 @@
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="60"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2619,7 +2638,7 @@
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="60"/>
+      <c r="C32" s="59"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2645,7 +2664,7 @@
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="60"/>
+      <c r="C33" s="59"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -2655,7 +2674,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="52">
+      <c r="H33" s="58">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -2671,7 +2690,7 @@
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="60"/>
+      <c r="C34" s="59"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -2681,9 +2700,13 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="55"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="36"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="J34" s="36">
+        <v>5</v>
+      </c>
       <c r="T34"/>
       <c r="Y34"/>
     </row>
@@ -2691,7 +2714,7 @@
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="61"/>
+      <c r="C35" s="60"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -2702,9 +2725,13 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="55"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="36"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="J35" s="36">
+        <v>5</v>
+      </c>
       <c r="T35"/>
       <c r="Y35"/>
     </row>
@@ -2712,7 +2739,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="71">
+      <c r="C36" s="58">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -2724,9 +2751,13 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="60"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="36"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="36">
+        <v>5</v>
+      </c>
       <c r="T36"/>
       <c r="Y36"/>
     </row>
@@ -2734,7 +2765,7 @@
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="59"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -2744,9 +2775,15 @@
       <c r="G37" s="3">
         <v>68</v>
       </c>
-      <c r="H37" s="60"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="36"/>
+      <c r="H37" s="52">
+        <v>46078</v>
+      </c>
+      <c r="I37" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="J37" s="36">
+        <v>5</v>
+      </c>
       <c r="T37"/>
       <c r="Y37"/>
     </row>
@@ -2754,7 +2791,7 @@
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="60"/>
+      <c r="C38" s="59"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -2764,7 +2801,7 @@
       <c r="G38" s="3">
         <v>69</v>
       </c>
-      <c r="H38" s="60"/>
+      <c r="H38" s="73"/>
       <c r="I38" s="41"/>
       <c r="J38" s="36"/>
       <c r="K38" s="2"/>
@@ -2776,7 +2813,7 @@
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="60"/>
+      <c r="C39" s="59"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -2787,7 +2824,7 @@
       <c r="G39" s="3">
         <v>70</v>
       </c>
-      <c r="H39" s="60"/>
+      <c r="H39" s="73"/>
       <c r="I39" s="41"/>
       <c r="J39" s="36"/>
       <c r="K39" s="2"/>
@@ -2799,7 +2836,7 @@
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="59"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -2809,7 +2846,7 @@
       <c r="G40" s="3">
         <v>71</v>
       </c>
-      <c r="H40" s="60"/>
+      <c r="H40" s="73"/>
       <c r="I40" s="41"/>
       <c r="J40" s="36"/>
       <c r="K40" s="2"/>
@@ -2821,7 +2858,7 @@
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="61"/>
+      <c r="C41" s="60"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -2831,7 +2868,7 @@
       <c r="G41" s="3">
         <v>72</v>
       </c>
-      <c r="H41" s="61"/>
+      <c r="H41" s="74"/>
       <c r="I41" s="41"/>
       <c r="J41" s="36"/>
       <c r="K41" s="2"/>
@@ -2843,7 +2880,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="71">
+      <c r="C42" s="58">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -2855,7 +2892,7 @@
       <c r="G42" s="3">
         <v>73</v>
       </c>
-      <c r="H42" s="71"/>
+      <c r="H42" s="58"/>
       <c r="I42" s="35"/>
       <c r="J42" s="36"/>
       <c r="K42" s="2"/>
@@ -2867,7 +2904,7 @@
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="60"/>
+      <c r="C43" s="59"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -2877,7 +2914,7 @@
       <c r="G43" s="3">
         <v>74</v>
       </c>
-      <c r="H43" s="60"/>
+      <c r="H43" s="59"/>
       <c r="I43" s="35"/>
       <c r="J43" s="36"/>
       <c r="K43" s="2"/>
@@ -2902,7 +2939,7 @@
       <c r="I44" s="39"/>
       <c r="J44" s="40">
         <f>SUM(J7:J43)</f>
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="K44" s="2"/>
       <c r="P44" s="2"/>
@@ -2912,15 +2949,6 @@
     <row r="45" spans="2:25" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H36:H41"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -2933,6 +2961,15 @@
     <mergeCell ref="H7:H12"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\OneDrive\문서\ALDrive\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shell\kang\done\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E375CC-7D63-4D96-AF17-9D3E7999311A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED6159F-2AFE-4755-B16D-C2E83203A8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="975" windowWidth="22725" windowHeight="13245" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -408,6 +408,10 @@
   </si>
   <si>
     <t>노승관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사성헌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1418,29 +1422,11 @@
     <xf numFmtId="176" fontId="7" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1454,6 +1440,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1472,11 +1473,14 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1838,45 +1842,45 @@
   <sheetData>
     <row r="1" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
       <c r="U2" s="49"/>
     </row>
     <row r="3" spans="2:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:25" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
-      <c r="R4" s="68"/>
-      <c r="S4" s="68"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
     </row>
     <row r="5" spans="2:25" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:25" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1904,12 +1908,12 @@
       <c r="J6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="65"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="59"/>
       <c r="T6"/>
       <c r="Y6"/>
     </row>
@@ -1917,7 +1921,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -1929,7 +1933,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -1957,7 +1961,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="59"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -1967,7 +1971,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="59"/>
+      <c r="H8" s="61"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -1993,7 +1997,7 @@
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="59"/>
+      <c r="C9" s="61"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2003,7 +2007,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="59"/>
+      <c r="H9" s="61"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2021,7 +2025,7 @@
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="60"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2031,7 +2035,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="59"/>
+      <c r="H10" s="61"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2049,7 +2053,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2061,7 +2065,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="59"/>
+      <c r="H11" s="61"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2084,7 +2088,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="56"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2094,7 +2098,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="60"/>
+      <c r="H12" s="62"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2108,7 +2112,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="56"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2118,7 +2122,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2127,10 +2131,10 @@
       <c r="J13" s="32">
         <v>5</v>
       </c>
-      <c r="L13" s="69" t="s">
+      <c r="L13" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="70"/>
+      <c r="M13" s="69"/>
       <c r="N13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2144,7 +2148,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="56"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2154,7 +2158,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="56"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2162,13 +2166,13 @@
         <v>5</v>
       </c>
       <c r="K14" s="51"/>
-      <c r="L14" s="71" t="s">
+      <c r="L14" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="M14" s="72"/>
+      <c r="M14" s="71"/>
       <c r="N14" s="25">
         <f>E44+J44</f>
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="O14" s="15"/>
       <c r="T14"/>
@@ -2178,7 +2182,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="56"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2188,17 +2192,17 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="57"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J15" s="32">
         <v>5</v>
       </c>
-      <c r="L15" s="71" t="s">
+      <c r="L15" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="72"/>
+      <c r="M15" s="71"/>
       <c r="N15" s="26">
         <f>N11</f>
         <v>1000</v>
@@ -2211,7 +2215,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2221,7 +2225,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2230,13 +2234,13 @@
       <c r="J16" s="32">
         <v>5</v>
       </c>
-      <c r="L16" s="61" t="s">
+      <c r="L16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="62"/>
+      <c r="M16" s="74"/>
       <c r="N16" s="27">
         <f>SUM(N14:N15)</f>
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>70</v>
@@ -2248,7 +2252,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2260,7 +2264,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="56"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2274,7 +2278,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="56"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2284,7 +2288,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="57"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2299,7 +2303,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="56"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2309,7 +2313,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2325,7 +2329,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="56"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2335,7 +2339,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="56"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2349,7 +2353,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="57"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2359,7 +2363,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="57"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2373,7 +2377,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2401,7 +2405,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="56"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2428,7 +2432,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="56"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2454,7 +2458,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="56"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2480,7 +2484,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="56"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2490,7 +2494,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2506,7 +2510,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="57"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2516,7 +2520,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="56"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2558,7 +2562,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="58">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2586,7 +2590,7 @@
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="59"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2612,7 +2616,7 @@
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="59"/>
+      <c r="C31" s="61"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2638,7 +2642,7 @@
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="59"/>
+      <c r="C32" s="61"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2664,7 +2668,7 @@
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="59"/>
+      <c r="C33" s="61"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -2674,7 +2678,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="58">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -2690,7 +2694,7 @@
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="59"/>
+      <c r="C34" s="61"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -2700,7 +2704,7 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="59"/>
+      <c r="H34" s="61"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
@@ -2714,7 +2718,7 @@
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="60"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -2725,7 +2729,7 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="59"/>
+      <c r="H35" s="61"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
@@ -2739,7 +2743,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="58">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -2751,7 +2755,7 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="59"/>
+      <c r="H36" s="61"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
@@ -2765,7 +2769,7 @@
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="59"/>
+      <c r="C37" s="61"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -2791,7 +2795,7 @@
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="59"/>
+      <c r="C38" s="61"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -2801,9 +2805,15 @@
       <c r="G38" s="3">
         <v>69</v>
       </c>
-      <c r="H38" s="73"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="36"/>
+      <c r="H38" s="52">
+        <v>46081</v>
+      </c>
+      <c r="I38" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="J38" s="36">
+        <v>5</v>
+      </c>
       <c r="K38" s="2"/>
       <c r="P38" s="2"/>
       <c r="T38"/>
@@ -2813,7 +2823,7 @@
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="59"/>
+      <c r="C39" s="61"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -2824,7 +2834,7 @@
       <c r="G39" s="3">
         <v>70</v>
       </c>
-      <c r="H39" s="73"/>
+      <c r="H39" s="55"/>
       <c r="I39" s="41"/>
       <c r="J39" s="36"/>
       <c r="K39" s="2"/>
@@ -2836,7 +2846,7 @@
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="59"/>
+      <c r="C40" s="61"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -2846,7 +2856,7 @@
       <c r="G40" s="3">
         <v>71</v>
       </c>
-      <c r="H40" s="73"/>
+      <c r="H40" s="55"/>
       <c r="I40" s="41"/>
       <c r="J40" s="36"/>
       <c r="K40" s="2"/>
@@ -2858,7 +2868,7 @@
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="60"/>
+      <c r="C41" s="62"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -2868,7 +2878,7 @@
       <c r="G41" s="3">
         <v>72</v>
       </c>
-      <c r="H41" s="74"/>
+      <c r="H41" s="56"/>
       <c r="I41" s="41"/>
       <c r="J41" s="36"/>
       <c r="K41" s="2"/>
@@ -2880,7 +2890,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="58">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -2892,7 +2902,7 @@
       <c r="G42" s="3">
         <v>73</v>
       </c>
-      <c r="H42" s="58"/>
+      <c r="H42" s="72"/>
       <c r="I42" s="35"/>
       <c r="J42" s="36"/>
       <c r="K42" s="2"/>
@@ -2904,7 +2914,7 @@
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="59"/>
+      <c r="C43" s="61"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -2914,7 +2924,7 @@
       <c r="G43" s="3">
         <v>74</v>
       </c>
-      <c r="H43" s="59"/>
+      <c r="H43" s="61"/>
       <c r="I43" s="35"/>
       <c r="J43" s="36"/>
       <c r="K43" s="2"/>
@@ -2939,7 +2949,7 @@
       <c r="I44" s="39"/>
       <c r="J44" s="40">
         <f>SUM(J7:J43)</f>
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K44" s="2"/>
       <c r="P44" s="2"/>
@@ -2949,6 +2959,15 @@
     <row r="45" spans="2:25" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -2961,15 +2980,6 @@
     <mergeCell ref="H7:H12"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shell\kang\done\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ch59\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7ED6159F-2AFE-4755-B16D-C2E83203A8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F80F135-7897-4846-AD6D-FDF63CF6FD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
+    <workbookView xWindow="4890" yWindow="1320" windowWidth="22725" windowHeight="13245" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -412,6 +412,10 @@
   </si>
   <si>
     <t>사성헌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마흥태</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2172,7 +2176,7 @@
       <c r="M14" s="71"/>
       <c r="N14" s="25">
         <f>E44+J44</f>
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="O14" s="15"/>
       <c r="T14"/>
@@ -2240,7 +2244,7 @@
       <c r="M16" s="74"/>
       <c r="N16" s="27">
         <f>SUM(N14:N15)</f>
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>70</v>
@@ -2834,9 +2838,15 @@
       <c r="G39" s="3">
         <v>70</v>
       </c>
-      <c r="H39" s="55"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="36"/>
+      <c r="H39" s="52">
+        <v>46085</v>
+      </c>
+      <c r="I39" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="J39" s="36">
+        <v>5</v>
+      </c>
       <c r="K39" s="2"/>
       <c r="P39" s="2"/>
       <c r="T39"/>
@@ -2949,7 +2959,7 @@
       <c r="I44" s="39"/>
       <c r="J44" s="40">
         <f>SUM(J7:J43)</f>
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K44" s="2"/>
       <c r="P44" s="2"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ch59\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F80F135-7897-4846-AD6D-FDF63CF6FD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F01691-01A5-4425-AAD9-43F0F3A893F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4890" yWindow="1320" windowWidth="22725" windowHeight="13245" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -416,6 +416,18 @@
   </si>
   <si>
     <t>마흥태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>민경식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노경태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김낙영</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1426,11 +1438,32 @@
     <xf numFmtId="176" fontId="7" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1444,47 +1477,26 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1846,45 +1858,45 @@
   <sheetData>
     <row r="1" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
+      <c r="O2" s="68"/>
       <c r="U2" s="49"/>
     </row>
     <row r="3" spans="2:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:25" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
     </row>
     <row r="5" spans="2:25" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:25" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1912,12 +1924,12 @@
       <c r="J6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="57" t="s">
+      <c r="L6" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="59"/>
+      <c r="M6" s="65"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="66"/>
       <c r="T6"/>
       <c r="Y6"/>
     </row>
@@ -1925,7 +1937,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -1937,7 +1949,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="67">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -1965,7 +1977,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="61"/>
+      <c r="C8" s="60"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -1975,7 +1987,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="61"/>
+      <c r="H8" s="60"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -2001,7 +2013,7 @@
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="61"/>
+      <c r="C9" s="60"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2011,7 +2023,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="61"/>
+      <c r="H9" s="60"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2029,7 +2041,7 @@
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="62"/>
+      <c r="C10" s="61"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2039,7 +2051,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="61"/>
+      <c r="H10" s="60"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2057,7 +2069,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="56">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2069,7 +2081,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="61"/>
+      <c r="H11" s="60"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2092,7 +2104,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="57"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2102,7 +2114,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="62"/>
+      <c r="H12" s="61"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2116,7 +2128,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="57"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2126,7 +2138,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="56">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2135,10 +2147,10 @@
       <c r="J13" s="32">
         <v>5</v>
       </c>
-      <c r="L13" s="68" t="s">
+      <c r="L13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="69"/>
+      <c r="M13" s="71"/>
       <c r="N13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2152,7 +2164,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="57"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2162,7 +2174,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="57"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2170,13 +2182,13 @@
         <v>5</v>
       </c>
       <c r="K14" s="51"/>
-      <c r="L14" s="70" t="s">
+      <c r="L14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="M14" s="71"/>
+      <c r="M14" s="73"/>
       <c r="N14" s="25">
         <f>E44+J44</f>
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="O14" s="15"/>
       <c r="T14"/>
@@ -2186,7 +2198,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="57"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2196,17 +2208,17 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="58"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J15" s="32">
         <v>5</v>
       </c>
-      <c r="L15" s="70" t="s">
+      <c r="L15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="71"/>
+      <c r="M15" s="73"/>
       <c r="N15" s="26">
         <f>N11</f>
         <v>1000</v>
@@ -2219,7 +2231,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="58"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2229,7 +2241,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="56">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2238,13 +2250,13 @@
       <c r="J16" s="32">
         <v>5</v>
       </c>
-      <c r="L16" s="73" t="s">
+      <c r="L16" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="74"/>
+      <c r="M16" s="63"/>
       <c r="N16" s="27">
         <f>SUM(N14:N15)</f>
-        <v>1352</v>
+        <v>1367</v>
       </c>
       <c r="O16" s="17" t="s">
         <v>70</v>
@@ -2256,7 +2268,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="56">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2268,7 +2280,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="57"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2282,7 +2294,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="57"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2292,7 +2304,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="58"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2307,7 +2319,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2317,7 +2329,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="56">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2333,7 +2345,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="57"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2343,7 +2355,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="57"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2357,7 +2369,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="58"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2367,7 +2379,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="58"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2381,7 +2393,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="56">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2409,7 +2421,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2436,7 +2448,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="57"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2462,7 +2474,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2488,7 +2500,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="57"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2498,7 +2510,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="56">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2514,7 +2526,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="58"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2524,7 +2536,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="57"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2566,7 +2578,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="59">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2594,7 +2606,7 @@
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="61"/>
+      <c r="C30" s="60"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2620,7 +2632,7 @@
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="61"/>
+      <c r="C31" s="60"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2646,7 +2658,7 @@
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="61"/>
+      <c r="C32" s="60"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2672,7 +2684,7 @@
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="61"/>
+      <c r="C33" s="60"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -2682,7 +2694,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="59">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -2698,7 +2710,7 @@
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="61"/>
+      <c r="C34" s="60"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -2708,7 +2720,7 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="61"/>
+      <c r="H34" s="60"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
@@ -2722,7 +2734,7 @@
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="62"/>
+      <c r="C35" s="61"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -2733,7 +2745,7 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="61"/>
+      <c r="H35" s="60"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
@@ -2747,7 +2759,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="59">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -2759,7 +2771,7 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="61"/>
+      <c r="H36" s="60"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
@@ -2773,7 +2785,7 @@
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="61"/>
+      <c r="C37" s="60"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -2799,7 +2811,7 @@
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="61"/>
+      <c r="C38" s="60"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -2827,7 +2839,7 @@
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="61"/>
+      <c r="C39" s="60"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -2856,7 +2868,7 @@
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="61"/>
+      <c r="C40" s="60"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -2866,9 +2878,15 @@
       <c r="G40" s="3">
         <v>71</v>
       </c>
-      <c r="H40" s="55"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="36"/>
+      <c r="H40" s="52">
+        <v>46089</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="J40" s="36">
+        <v>5</v>
+      </c>
       <c r="K40" s="2"/>
       <c r="P40" s="2"/>
       <c r="T40"/>
@@ -2878,7 +2896,7 @@
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="62"/>
+      <c r="C41" s="61"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -2888,9 +2906,15 @@
       <c r="G41" s="3">
         <v>72</v>
       </c>
-      <c r="H41" s="56"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="36"/>
+      <c r="H41" s="55">
+        <v>46093</v>
+      </c>
+      <c r="I41" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="J41" s="36">
+        <v>5</v>
+      </c>
       <c r="K41" s="2"/>
       <c r="P41" s="2"/>
       <c r="T41"/>
@@ -2900,7 +2924,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="59">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -2912,9 +2936,15 @@
       <c r="G42" s="3">
         <v>73</v>
       </c>
-      <c r="H42" s="72"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="36"/>
+      <c r="H42" s="52">
+        <v>46097</v>
+      </c>
+      <c r="I42" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="J42" s="36">
+        <v>5</v>
+      </c>
       <c r="K42" s="2"/>
       <c r="P42" s="2"/>
       <c r="T42"/>
@@ -2924,7 +2954,7 @@
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="61"/>
+      <c r="C43" s="60"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -2934,7 +2964,7 @@
       <c r="G43" s="3">
         <v>74</v>
       </c>
-      <c r="H43" s="61"/>
+      <c r="H43" s="74"/>
       <c r="I43" s="35"/>
       <c r="J43" s="36"/>
       <c r="K43" s="2"/>
@@ -2959,7 +2989,7 @@
       <c r="I44" s="39"/>
       <c r="J44" s="40">
         <f>SUM(J7:J43)</f>
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="K44" s="2"/>
       <c r="P44" s="2"/>
@@ -2968,16 +2998,7 @@
     </row>
     <row r="45" spans="2:25" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
+  <mergeCells count="20">
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -2990,6 +3011,14 @@
     <mergeCell ref="H7:H12"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ch59\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F01691-01A5-4425-AAD9-43F0F3A893F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49946B89-C5AB-4F80-99CB-FAABFCA39CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="1320" windowWidth="22725" windowHeight="13245" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="96">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -428,6 +428,22 @@
   </si>
   <si>
     <t>김낙영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이진구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이계판</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤석우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김진수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -621,7 +637,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1268,13 +1284,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF002060"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF002060"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF002060"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF002060"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1441,28 +1472,7 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1477,6 +1487,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1495,8 +1520,20 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1819,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC16636-847A-47F1-BA3B-A88365FF7E52}">
-  <dimension ref="B1:Y45"/>
+  <dimension ref="B1:AD45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.375" customWidth="1"/>
@@ -1832,74 +1869,86 @@
     <col min="8" max="8" width="11.625" customWidth="1"/>
     <col min="9" max="9" width="8.375" customWidth="1"/>
     <col min="10" max="10" width="5.75" customWidth="1"/>
-    <col min="11" max="11" width="8.125" customWidth="1"/>
-    <col min="12" max="12" width="9.875" customWidth="1"/>
-    <col min="13" max="13" width="8.75" customWidth="1"/>
-    <col min="14" max="14" width="10.5" customWidth="1"/>
-    <col min="15" max="15" width="13.25" customWidth="1"/>
-    <col min="16" max="16" width="7.875" customWidth="1"/>
-    <col min="17" max="17" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="1.375" customWidth="1"/>
-    <col min="19" max="19" width="2.125" customWidth="1"/>
-    <col min="20" max="20" width="10.125" style="2" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5" customWidth="1"/>
-    <col min="22" max="22" width="7.75" customWidth="1"/>
-    <col min="23" max="23" width="8.75" customWidth="1"/>
-    <col min="24" max="24" width="13.75" customWidth="1"/>
-    <col min="25" max="25" width="11.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="2.875" customWidth="1"/>
+    <col min="12" max="12" width="5.125" customWidth="1"/>
+    <col min="13" max="13" width="11.625" customWidth="1"/>
+    <col min="14" max="14" width="8.375" customWidth="1"/>
+    <col min="15" max="15" width="5.75" customWidth="1"/>
+    <col min="16" max="16" width="8.125" customWidth="1"/>
+    <col min="17" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="8.75" customWidth="1"/>
+    <col min="19" max="19" width="10.5" customWidth="1"/>
+    <col min="20" max="20" width="13.25" customWidth="1"/>
+    <col min="21" max="21" width="7.875" customWidth="1"/>
+    <col min="22" max="22" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.375" customWidth="1"/>
+    <col min="24" max="24" width="2.125" customWidth="1"/>
+    <col min="25" max="25" width="10.125" style="2" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="10.5" customWidth="1"/>
-    <col min="27" max="27" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="1.25" customWidth="1"/>
-    <col min="29" max="29" width="10.375" customWidth="1"/>
-    <col min="30" max="30" width="7.375" customWidth="1"/>
-    <col min="31" max="31" width="9.875" customWidth="1"/>
-    <col min="32" max="32" width="11.5" customWidth="1"/>
+    <col min="27" max="27" width="7.75" customWidth="1"/>
+    <col min="28" max="28" width="8.75" customWidth="1"/>
+    <col min="29" max="29" width="13.75" customWidth="1"/>
+    <col min="30" max="30" width="11.25" style="2" customWidth="1"/>
+    <col min="31" max="31" width="10.5" customWidth="1"/>
+    <col min="32" max="32" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="1.25" customWidth="1"/>
+    <col min="34" max="34" width="10.375" customWidth="1"/>
+    <col min="35" max="35" width="7.375" customWidth="1"/>
+    <col min="36" max="36" width="9.875" customWidth="1"/>
+    <col min="37" max="37" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="68" t="s">
+    <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
-      <c r="U2" s="49"/>
-    </row>
-    <row r="3" spans="2:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:25" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="C4" s="69" t="s">
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="Z2" s="49"/>
+    </row>
+    <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B4" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="69"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="69"/>
-      <c r="S4" s="69"/>
-    </row>
-    <row r="5" spans="2:25" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="2:25" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+    </row>
+    <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
@@ -1924,20 +1973,32 @@
       <c r="J6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="64" t="s">
+      <c r="L6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="66"/>
-      <c r="T6"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="59"/>
       <c r="Y6"/>
-    </row>
-    <row r="7" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD6"/>
+    </row>
+    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -1949,7 +2010,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="67">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -1958,26 +2019,38 @@
       <c r="J7" s="32">
         <v>5</v>
       </c>
-      <c r="L7" s="42" t="s">
+      <c r="L7" s="3">
+        <v>75</v>
+      </c>
+      <c r="M7" s="76">
+        <v>46108</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="M7" s="43" t="s">
+      <c r="R7" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="44" t="s">
+      <c r="S7" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="T7"/>
+      <c r="T7" s="45" t="s">
+        <v>5</v>
+      </c>
       <c r="Y7"/>
-    </row>
-    <row r="8" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD7"/>
+    </row>
+    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="60"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -1987,33 +2060,45 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="60"/>
+      <c r="H8" s="61"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
       <c r="J8" s="32">
         <v>5</v>
       </c>
-      <c r="L8" s="46">
+      <c r="L8" s="3">
+        <v>76</v>
+      </c>
+      <c r="M8" s="52">
+        <v>46109</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="O8" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="46">
         <v>46020</v>
       </c>
-      <c r="M8" s="47" t="s">
+      <c r="R8" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="N8" s="44">
+      <c r="S8" s="44">
         <v>1000</v>
       </c>
-      <c r="O8" s="45" t="s">
+      <c r="T8" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="T8"/>
       <c r="Y8"/>
-    </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD8"/>
+    </row>
+    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="60"/>
+      <c r="C9" s="61"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2023,25 +2108,37 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="60"/>
+      <c r="H9" s="61"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
       <c r="J9" s="32">
         <v>5</v>
       </c>
-      <c r="L9" s="46"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="45"/>
-      <c r="T9"/>
+      <c r="L9" s="3">
+        <v>77</v>
+      </c>
+      <c r="M9" s="52">
+        <v>46111</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="45"/>
       <c r="Y9"/>
-    </row>
-    <row r="10" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD9"/>
+    </row>
+    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="61"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2051,25 +2148,31 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="60"/>
+      <c r="H10" s="61"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
       <c r="J10" s="32">
         <v>5</v>
       </c>
-      <c r="L10" s="23"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="30"/>
-      <c r="T10"/>
+      <c r="L10" s="3">
+        <v>78</v>
+      </c>
+      <c r="M10" s="56"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="32"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="30"/>
       <c r="Y10"/>
-    </row>
-    <row r="11" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD10"/>
+    </row>
+    <row r="11" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2081,30 +2184,36 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="60"/>
+      <c r="H11" s="61"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
       <c r="J11" s="32">
         <v>10</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="10" t="s">
+      <c r="L11" s="3">
+        <v>79</v>
+      </c>
+      <c r="M11" s="56"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="32"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N11" s="29">
-        <f>SUM(N7:N10)</f>
+      <c r="S11" s="29">
+        <f>SUM(S7:S10)</f>
         <v>1000</v>
       </c>
-      <c r="O11" s="11"/>
-      <c r="T11"/>
+      <c r="T11" s="11"/>
       <c r="Y11"/>
-    </row>
-    <row r="12" spans="2:25" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD11"/>
+    </row>
+    <row r="12" spans="2:30" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="57"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2114,21 +2223,27 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="61"/>
+      <c r="H12" s="62"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
       <c r="J12" s="32">
         <v>5</v>
       </c>
-      <c r="T12"/>
+      <c r="L12" s="3">
+        <v>80</v>
+      </c>
+      <c r="M12" s="55"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="32"/>
       <c r="Y12"/>
-    </row>
-    <row r="13" spans="2:25" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="AD12"/>
+    </row>
+    <row r="13" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="57"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2138,7 +2253,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="56">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2147,24 +2262,30 @@
       <c r="J13" s="32">
         <v>5</v>
       </c>
-      <c r="L13" s="70" t="s">
+      <c r="L13" s="3">
+        <v>81</v>
+      </c>
+      <c r="M13" s="63"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="32"/>
+      <c r="Q13" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="M13" s="71"/>
-      <c r="N13" s="18" t="s">
+      <c r="R13" s="69"/>
+      <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="O13" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="T13"/>
+      <c r="T13" s="19" t="s">
+        <v>5</v>
+      </c>
       <c r="Y13"/>
-    </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD13"/>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="57"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2174,7 +2295,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="57"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2182,23 +2303,30 @@
         <v>5</v>
       </c>
       <c r="K14" s="51"/>
-      <c r="L14" s="72" t="s">
+      <c r="L14" s="3">
+        <v>82</v>
+      </c>
+      <c r="M14" s="64"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="75"/>
+      <c r="Q14" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="M14" s="73"/>
-      <c r="N14" s="25">
-        <f>E44+J44</f>
-        <v>367</v>
-      </c>
-      <c r="O14" s="15"/>
-      <c r="T14"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="25">
+        <f>E44+J44+O44</f>
+        <v>387</v>
+      </c>
+      <c r="T14" s="15"/>
       <c r="Y14"/>
-    </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD14"/>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="57"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2208,30 +2336,36 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="58"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J15" s="32">
         <v>5</v>
       </c>
-      <c r="L15" s="72" t="s">
+      <c r="L15" s="3">
+        <v>83</v>
+      </c>
+      <c r="M15" s="65"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="32"/>
+      <c r="Q15" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="M15" s="73"/>
-      <c r="N15" s="26">
-        <f>N11</f>
+      <c r="R15" s="71"/>
+      <c r="S15" s="26">
+        <f>S11</f>
         <v>1000</v>
       </c>
-      <c r="O15" s="16"/>
-      <c r="T15"/>
+      <c r="T15" s="16"/>
       <c r="Y15"/>
-    </row>
-    <row r="16" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD15"/>
+    </row>
+    <row r="16" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2241,7 +2375,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="56">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2250,25 +2384,31 @@
       <c r="J16" s="32">
         <v>5</v>
       </c>
-      <c r="L16" s="62" t="s">
+      <c r="L16" s="3">
+        <v>84</v>
+      </c>
+      <c r="M16" s="63"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="32"/>
+      <c r="Q16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="M16" s="63"/>
-      <c r="N16" s="27">
-        <f>SUM(N14:N15)</f>
-        <v>1367</v>
-      </c>
-      <c r="O16" s="17" t="s">
+      <c r="R16" s="74"/>
+      <c r="S16" s="27">
+        <f>SUM(S14:S15)</f>
+        <v>1387</v>
+      </c>
+      <c r="T16" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="T16"/>
       <c r="Y16"/>
-    </row>
-    <row r="17" spans="2:25" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="AD16"/>
+    </row>
+    <row r="17" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="56">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2280,21 +2420,27 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="57"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
       <c r="J17" s="32">
         <v>5</v>
       </c>
-      <c r="T17"/>
+      <c r="L17" s="3">
+        <v>85</v>
+      </c>
+      <c r="M17" s="64"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="32"/>
       <c r="Y17"/>
-    </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD17"/>
+    </row>
+    <row r="18" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="57"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2304,22 +2450,28 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="58"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
       <c r="J18" s="32">
         <v>5</v>
       </c>
-      <c r="N18" s="12"/>
-      <c r="T18"/>
+      <c r="L18" s="3">
+        <v>86</v>
+      </c>
+      <c r="M18" s="65"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="32"/>
+      <c r="S18" s="12"/>
       <c r="Y18"/>
-    </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD18"/>
+    </row>
+    <row r="19" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="57"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2329,7 +2481,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="56">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2338,14 +2490,20 @@
       <c r="J19" s="32">
         <v>5</v>
       </c>
-      <c r="T19"/>
+      <c r="L19" s="3">
+        <v>87</v>
+      </c>
+      <c r="M19" s="63"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="32"/>
       <c r="Y19"/>
-    </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD19"/>
+    </row>
+    <row r="20" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="57"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2355,21 +2513,27 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="57"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
       <c r="J20" s="32">
         <v>5</v>
       </c>
-      <c r="T20"/>
+      <c r="L20" s="3">
+        <v>88</v>
+      </c>
+      <c r="M20" s="64"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="32"/>
       <c r="Y20"/>
-    </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD20"/>
+    </row>
+    <row r="21" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="58"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2379,21 +2543,27 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="58"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
       <c r="J21" s="32">
         <v>3</v>
       </c>
-      <c r="T21"/>
+      <c r="L21" s="3">
+        <v>89</v>
+      </c>
+      <c r="M21" s="65"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="32"/>
       <c r="Y21"/>
-    </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD21"/>
+    </row>
+    <row r="22" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2414,14 +2584,20 @@
       <c r="J22" s="32">
         <v>5</v>
       </c>
-      <c r="T22"/>
+      <c r="L22" s="3">
+        <v>90</v>
+      </c>
+      <c r="M22" s="54"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="32"/>
       <c r="Y22"/>
-    </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD22"/>
+    </row>
+    <row r="23" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="57"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2440,15 +2616,21 @@
       <c r="J23" s="32">
         <v>5</v>
       </c>
-      <c r="Q23" s="7"/>
-      <c r="T23"/>
+      <c r="L23" s="3">
+        <v>91</v>
+      </c>
+      <c r="M23" s="54"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="32"/>
+      <c r="V23" s="7"/>
       <c r="Y23"/>
-    </row>
-    <row r="24" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD23"/>
+    </row>
+    <row r="24" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="57"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2467,14 +2649,20 @@
       <c r="J24" s="32">
         <v>5</v>
       </c>
-      <c r="T24"/>
+      <c r="L24" s="3">
+        <v>92</v>
+      </c>
+      <c r="M24" s="54"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="32"/>
       <c r="Y24"/>
-    </row>
-    <row r="25" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD24"/>
+    </row>
+    <row r="25" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="57"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2493,14 +2681,20 @@
       <c r="J25" s="32">
         <v>5</v>
       </c>
-      <c r="T25"/>
+      <c r="L25" s="3">
+        <v>93</v>
+      </c>
+      <c r="M25" s="53"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="32"/>
       <c r="Y25"/>
-    </row>
-    <row r="26" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD25"/>
+    </row>
+    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="57"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2510,7 +2704,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="56">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2519,14 +2713,20 @@
       <c r="J26" s="32">
         <v>5</v>
       </c>
-      <c r="T26"/>
+      <c r="L26" s="3">
+        <v>94</v>
+      </c>
+      <c r="M26" s="63"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="32"/>
       <c r="Y26"/>
-    </row>
-    <row r="27" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD26"/>
+    </row>
+    <row r="27" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="58"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2536,17 +2736,23 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="57"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
       <c r="J27" s="36">
         <v>5</v>
       </c>
-      <c r="T27"/>
+      <c r="L27" s="3">
+        <v>95</v>
+      </c>
+      <c r="M27" s="64"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="36"/>
       <c r="Y27"/>
-    </row>
-    <row r="28" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD27"/>
+    </row>
+    <row r="28" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <v>22</v>
       </c>
@@ -2571,14 +2777,20 @@
       <c r="J28" s="36">
         <v>5</v>
       </c>
-      <c r="T28"/>
+      <c r="L28" s="3">
+        <v>96</v>
+      </c>
+      <c r="M28" s="52"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="36"/>
       <c r="Y28"/>
-    </row>
-    <row r="29" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD28"/>
+    </row>
+    <row r="29" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2599,14 +2811,20 @@
       <c r="J29" s="36">
         <v>5</v>
       </c>
-      <c r="T29"/>
+      <c r="L29" s="3">
+        <v>97</v>
+      </c>
+      <c r="M29" s="52"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="36"/>
       <c r="Y29"/>
-    </row>
-    <row r="30" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD29"/>
+    </row>
+    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="60"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2625,14 +2843,20 @@
       <c r="J30" s="36">
         <v>5</v>
       </c>
-      <c r="T30"/>
+      <c r="L30" s="3">
+        <v>98</v>
+      </c>
+      <c r="M30" s="52"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="36"/>
       <c r="Y30"/>
-    </row>
-    <row r="31" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD30"/>
+    </row>
+    <row r="31" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="60"/>
+      <c r="C31" s="61"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2651,14 +2875,20 @@
       <c r="J31" s="36">
         <v>5</v>
       </c>
-      <c r="T31"/>
+      <c r="L31" s="3">
+        <v>99</v>
+      </c>
+      <c r="M31" s="52"/>
+      <c r="N31" s="37"/>
+      <c r="O31" s="36"/>
       <c r="Y31"/>
-    </row>
-    <row r="32" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD31"/>
+    </row>
+    <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="60"/>
+      <c r="C32" s="61"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2677,14 +2907,20 @@
       <c r="J32" s="36">
         <v>5</v>
       </c>
-      <c r="T32"/>
+      <c r="L32" s="3">
+        <v>100</v>
+      </c>
+      <c r="M32" s="52"/>
+      <c r="N32" s="37"/>
+      <c r="O32" s="36"/>
       <c r="Y32"/>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD32"/>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="60"/>
+      <c r="C33" s="61"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -2694,7 +2930,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="59">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -2703,14 +2939,20 @@
       <c r="J33" s="36">
         <v>5</v>
       </c>
-      <c r="T33"/>
+      <c r="L33" s="3">
+        <v>101</v>
+      </c>
+      <c r="M33" s="72"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="36"/>
       <c r="Y33"/>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD33"/>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="60"/>
+      <c r="C34" s="61"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -2720,21 +2962,27 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="60"/>
+      <c r="H34" s="61"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
       <c r="J34" s="36">
         <v>5</v>
       </c>
-      <c r="T34"/>
+      <c r="L34" s="3">
+        <v>102</v>
+      </c>
+      <c r="M34" s="61"/>
+      <c r="N34" s="37"/>
+      <c r="O34" s="36"/>
       <c r="Y34"/>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD34"/>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="61"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -2745,21 +2993,27 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="60"/>
+      <c r="H35" s="61"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
       <c r="J35" s="36">
         <v>5</v>
       </c>
-      <c r="T35"/>
+      <c r="L35" s="3">
+        <v>103</v>
+      </c>
+      <c r="M35" s="61"/>
+      <c r="N35" s="37"/>
+      <c r="O35" s="36"/>
       <c r="Y35"/>
-    </row>
-    <row r="36" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD35"/>
+    </row>
+    <row r="36" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -2771,21 +3025,27 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="60"/>
+      <c r="H36" s="61"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
       <c r="J36" s="36">
         <v>5</v>
       </c>
-      <c r="T36"/>
+      <c r="L36" s="3">
+        <v>104</v>
+      </c>
+      <c r="M36" s="61"/>
+      <c r="N36" s="37"/>
+      <c r="O36" s="36"/>
       <c r="Y36"/>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD36"/>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="61"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -2804,14 +3064,20 @@
       <c r="J37" s="36">
         <v>5</v>
       </c>
-      <c r="T37"/>
+      <c r="L37" s="3">
+        <v>105</v>
+      </c>
+      <c r="M37" s="52"/>
+      <c r="N37" s="50"/>
+      <c r="O37" s="36"/>
       <c r="Y37"/>
-    </row>
-    <row r="38" spans="2:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AD37"/>
+    </row>
+    <row r="38" spans="2:30" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="60"/>
+      <c r="C38" s="61"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -2831,15 +3097,22 @@
         <v>5</v>
       </c>
       <c r="K38" s="2"/>
+      <c r="L38" s="3">
+        <v>106</v>
+      </c>
+      <c r="M38" s="52"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="36"/>
       <c r="P38" s="2"/>
-      <c r="T38"/>
+      <c r="U38" s="2"/>
       <c r="Y38"/>
-    </row>
-    <row r="39" spans="2:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="AD38"/>
+    </row>
+    <row r="39" spans="2:30" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="60"/>
+      <c r="C39" s="61"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -2860,15 +3133,22 @@
         <v>5</v>
       </c>
       <c r="K39" s="2"/>
+      <c r="L39" s="3">
+        <v>107</v>
+      </c>
+      <c r="M39" s="52"/>
+      <c r="N39" s="41"/>
+      <c r="O39" s="36"/>
       <c r="P39" s="2"/>
-      <c r="T39"/>
+      <c r="U39" s="2"/>
       <c r="Y39"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD39"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="60"/>
+      <c r="C40" s="61"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -2888,15 +3168,22 @@
         <v>5</v>
       </c>
       <c r="K40" s="2"/>
+      <c r="L40" s="3">
+        <v>108</v>
+      </c>
+      <c r="M40" s="52"/>
+      <c r="N40" s="41"/>
+      <c r="O40" s="36"/>
       <c r="P40" s="2"/>
-      <c r="T40"/>
+      <c r="U40" s="2"/>
       <c r="Y40"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD40"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="61"/>
+      <c r="C41" s="62"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -2916,15 +3203,22 @@
         <v>5</v>
       </c>
       <c r="K41" s="2"/>
+      <c r="L41" s="3">
+        <v>109</v>
+      </c>
+      <c r="M41" s="55"/>
+      <c r="N41" s="41"/>
+      <c r="O41" s="36"/>
       <c r="P41" s="2"/>
-      <c r="T41"/>
+      <c r="U41" s="2"/>
       <c r="Y41"/>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="AD41"/>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="59">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -2946,15 +3240,22 @@
         <v>5</v>
       </c>
       <c r="K42" s="2"/>
+      <c r="L42" s="3">
+        <v>110</v>
+      </c>
+      <c r="M42" s="52"/>
+      <c r="N42" s="35"/>
+      <c r="O42" s="36"/>
       <c r="P42" s="2"/>
-      <c r="T42"/>
+      <c r="U42" s="2"/>
       <c r="Y42"/>
-    </row>
-    <row r="43" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD42"/>
+    </row>
+    <row r="43" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="60"/>
+      <c r="C43" s="61"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -2964,15 +3265,28 @@
       <c r="G43" s="3">
         <v>74</v>
       </c>
-      <c r="H43" s="74"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="36"/>
+      <c r="H43" s="56">
+        <v>46099</v>
+      </c>
+      <c r="I43" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="J43" s="36">
+        <v>5</v>
+      </c>
       <c r="K43" s="2"/>
+      <c r="L43" s="3">
+        <v>111</v>
+      </c>
+      <c r="M43" s="56"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="36"/>
       <c r="P43" s="2"/>
-      <c r="T43"/>
+      <c r="U43" s="2"/>
       <c r="Y43"/>
-    </row>
-    <row r="44" spans="2:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AD43"/>
+    </row>
+    <row r="44" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="20"/>
       <c r="C44" s="38" t="s">
         <v>69</v>
@@ -2989,38 +3303,53 @@
       <c r="I44" s="39"/>
       <c r="J44" s="40">
         <f>SUM(J7:J43)</f>
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K44" s="2"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="N44" s="39"/>
+      <c r="O44" s="40">
+        <f>SUM(O7:O43)</f>
+        <v>15</v>
+      </c>
       <c r="P44" s="2"/>
-      <c r="T44"/>
+      <c r="U44" s="2"/>
       <c r="Y44"/>
-    </row>
-    <row r="45" spans="2:25" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="AD44"/>
+    </row>
+    <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="C4:S4"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="H7:H12"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="H16:H18"/>
+  <mergeCells count="25">
     <mergeCell ref="C22:C27"/>
     <mergeCell ref="C29:C35"/>
     <mergeCell ref="C36:C41"/>
     <mergeCell ref="C42:C43"/>
-    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="Q16:R16"/>
     <mergeCell ref="H19:H21"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="M19:M21"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M33:M36"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="H7:H12"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="M13:M15"/>
+    <mergeCell ref="B4:T4"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <picture r:id="rId2"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49946B89-C5AB-4F80-99CB-FAABFCA39CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65A470BB-E6A0-4D1D-9FAE-AFE4D9FE724D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="101">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -445,6 +445,26 @@
   <si>
     <t>김진수</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최상면</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>신기완</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>최병승</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>유기현</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>서성원</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1305,7 +1325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1475,6 +1495,33 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1487,53 +1534,32 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1900,52 +1926,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
-      <c r="P4" s="67"/>
-      <c r="Q4" s="67"/>
-      <c r="R4" s="67"/>
-      <c r="S4" s="67"/>
-      <c r="T4" s="67"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -1985,12 +2011,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="59"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="68"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -1998,7 +2024,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="69" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2010,7 +2036,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="69">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2022,7 +2048,7 @@
       <c r="L7" s="3">
         <v>75</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="57">
         <v>46108</v>
       </c>
       <c r="N7" s="31" t="s">
@@ -2050,7 +2076,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="61"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -2060,7 +2086,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="61"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -2098,7 +2124,7 @@
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="61"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2108,7 +2134,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="61"/>
+      <c r="H9" s="62"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2138,7 +2164,7 @@
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="62"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2148,7 +2174,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="61"/>
+      <c r="H10" s="62"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2158,9 +2184,15 @@
       <c r="L10" s="3">
         <v>78</v>
       </c>
-      <c r="M10" s="56"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="32"/>
+      <c r="M10" s="52">
+        <v>46116</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="32">
+        <v>5</v>
+      </c>
       <c r="Q10" s="23"/>
       <c r="R10" s="24"/>
       <c r="S10" s="28"/>
@@ -2172,7 +2204,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="58">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2184,7 +2216,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="61"/>
+      <c r="H11" s="62"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2194,9 +2226,15 @@
       <c r="L11" s="3">
         <v>79</v>
       </c>
-      <c r="M11" s="56"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="32"/>
+      <c r="M11" s="52">
+        <v>46117</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" s="32">
+        <v>5</v>
+      </c>
       <c r="Q11" s="9"/>
       <c r="R11" s="10" t="s">
         <v>4</v>
@@ -2213,7 +2251,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2223,7 +2261,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="62"/>
+      <c r="H12" s="63"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2233,9 +2271,15 @@
       <c r="L12" s="3">
         <v>80</v>
       </c>
-      <c r="M12" s="55"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="32"/>
+      <c r="M12" s="52">
+        <v>46123</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="O12" s="32">
+        <v>5</v>
+      </c>
       <c r="Y12"/>
       <c r="AD12"/>
     </row>
@@ -2243,7 +2287,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2253,7 +2297,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="58">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2265,13 +2309,19 @@
       <c r="L13" s="3">
         <v>81</v>
       </c>
-      <c r="M13" s="63"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="32"/>
-      <c r="Q13" s="68" t="s">
+      <c r="M13" s="52">
+        <v>46125</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="O13" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="69"/>
+      <c r="R13" s="72"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2285,7 +2335,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2295,7 +2345,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="59"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2306,17 +2356,22 @@
       <c r="L14" s="3">
         <v>82</v>
       </c>
-      <c r="M14" s="64"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="70" t="s">
+      <c r="M14" s="52">
+        <v>46127</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="O14" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="71"/>
+      <c r="R14" s="74"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2326,7 +2381,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2336,7 +2391,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2346,13 +2401,13 @@
       <c r="L15" s="3">
         <v>83</v>
       </c>
-      <c r="M15" s="65"/>
+      <c r="M15" s="78"/>
       <c r="N15" s="34"/>
       <c r="O15" s="32"/>
-      <c r="Q15" s="70" t="s">
+      <c r="Q15" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="71"/>
+      <c r="R15" s="74"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1000</v>
@@ -2365,7 +2420,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="60"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2375,7 +2430,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="58">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2387,16 +2442,16 @@
       <c r="L16" s="3">
         <v>84</v>
       </c>
-      <c r="M16" s="63"/>
+      <c r="M16" s="76"/>
       <c r="N16" s="34"/>
       <c r="O16" s="32"/>
-      <c r="Q16" s="73" t="s">
+      <c r="Q16" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="74"/>
+      <c r="R16" s="65"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1387</v>
+        <v>1412</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2408,7 +2463,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="58">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2420,7 +2475,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="59"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2430,7 +2485,7 @@
       <c r="L17" s="3">
         <v>85</v>
       </c>
-      <c r="M17" s="64"/>
+      <c r="M17" s="77"/>
       <c r="N17" s="34"/>
       <c r="O17" s="32"/>
       <c r="Y17"/>
@@ -2440,7 +2495,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2450,7 +2505,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="60"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2460,7 +2515,7 @@
       <c r="L18" s="3">
         <v>86</v>
       </c>
-      <c r="M18" s="65"/>
+      <c r="M18" s="78"/>
       <c r="N18" s="34"/>
       <c r="O18" s="32"/>
       <c r="S18" s="12"/>
@@ -2471,7 +2526,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2481,7 +2536,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="58">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2493,7 +2548,7 @@
       <c r="L19" s="3">
         <v>87</v>
       </c>
-      <c r="M19" s="63"/>
+      <c r="M19" s="76"/>
       <c r="N19" s="34"/>
       <c r="O19" s="32"/>
       <c r="Y19"/>
@@ -2503,7 +2558,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2513,7 +2568,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="59"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2523,7 +2578,7 @@
       <c r="L20" s="3">
         <v>88</v>
       </c>
-      <c r="M20" s="64"/>
+      <c r="M20" s="77"/>
       <c r="N20" s="35"/>
       <c r="O20" s="32"/>
       <c r="Y20"/>
@@ -2533,7 +2588,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2543,7 +2598,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="60"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2553,7 +2608,7 @@
       <c r="L21" s="3">
         <v>89</v>
       </c>
-      <c r="M21" s="65"/>
+      <c r="M21" s="78"/>
       <c r="N21" s="35"/>
       <c r="O21" s="32"/>
       <c r="Y21"/>
@@ -2563,7 +2618,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="58">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2597,7 +2652,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2630,7 +2685,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2662,7 +2717,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="59"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2694,7 +2749,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="59"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2704,7 +2759,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="58">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2716,7 +2771,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="63"/>
+      <c r="M26" s="58"/>
       <c r="N26" s="34"/>
       <c r="O26" s="32"/>
       <c r="Y26"/>
@@ -2726,7 +2781,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2736,7 +2791,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="59"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2746,7 +2801,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="64"/>
+      <c r="M27" s="59"/>
       <c r="N27" s="34"/>
       <c r="O27" s="36"/>
       <c r="Y27"/>
@@ -2790,7 +2845,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="61">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2824,7 +2879,7 @@
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="61"/>
+      <c r="C30" s="62"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2856,7 +2911,7 @@
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="61"/>
+      <c r="C31" s="62"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2888,7 +2943,7 @@
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="61"/>
+      <c r="C32" s="62"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2920,7 +2975,7 @@
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="61"/>
+      <c r="C33" s="62"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -2930,7 +2985,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="61">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -2942,7 +2997,7 @@
       <c r="L33" s="3">
         <v>101</v>
       </c>
-      <c r="M33" s="72"/>
+      <c r="M33" s="61"/>
       <c r="N33" s="34"/>
       <c r="O33" s="36"/>
       <c r="Y33"/>
@@ -2952,7 +3007,7 @@
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="61"/>
+      <c r="C34" s="62"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -2962,7 +3017,7 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="61"/>
+      <c r="H34" s="62"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
@@ -2972,7 +3027,7 @@
       <c r="L34" s="3">
         <v>102</v>
       </c>
-      <c r="M34" s="61"/>
+      <c r="M34" s="62"/>
       <c r="N34" s="37"/>
       <c r="O34" s="36"/>
       <c r="Y34"/>
@@ -2982,7 +3037,7 @@
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="62"/>
+      <c r="C35" s="63"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -2993,7 +3048,7 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="61"/>
+      <c r="H35" s="62"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
@@ -3003,7 +3058,7 @@
       <c r="L35" s="3">
         <v>103</v>
       </c>
-      <c r="M35" s="61"/>
+      <c r="M35" s="62"/>
       <c r="N35" s="37"/>
       <c r="O35" s="36"/>
       <c r="Y35"/>
@@ -3013,7 +3068,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="61">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3025,7 +3080,7 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="61"/>
+      <c r="H36" s="62"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
@@ -3035,7 +3090,7 @@
       <c r="L36" s="3">
         <v>104</v>
       </c>
-      <c r="M36" s="61"/>
+      <c r="M36" s="62"/>
       <c r="N36" s="37"/>
       <c r="O36" s="36"/>
       <c r="Y36"/>
@@ -3045,7 +3100,7 @@
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="61"/>
+      <c r="C37" s="62"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -3077,7 +3132,7 @@
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="61"/>
+      <c r="C38" s="62"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -3112,7 +3167,7 @@
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="61"/>
+      <c r="C39" s="62"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -3148,7 +3203,7 @@
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="61"/>
+      <c r="C40" s="62"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -3183,7 +3238,7 @@
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="62"/>
+      <c r="C41" s="63"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -3218,7 +3273,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="61">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3255,7 +3310,7 @@
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="61"/>
+      <c r="C43" s="62"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -3313,7 +3368,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3322,19 +3377,7 @@
     </row>
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="M33:M36"/>
+  <mergeCells count="22">
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3346,8 +3389,17 @@
     <mergeCell ref="H7:H12"/>
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
-    <mergeCell ref="M13:M15"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M33:M36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65A470BB-E6A0-4D1D-9FAE-AFE4D9FE724D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F54B860-3A80-4FB0-BB81-053D8DF48806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -464,6 +464,14 @@
   </si>
   <si>
     <t>서성원</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>황덕하</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이원석</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1325,7 +1333,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1498,6 +1506,12 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1551,15 +1565,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1926,52 +1931,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
+      <c r="R2" s="72"/>
+      <c r="S2" s="72"/>
+      <c r="T2" s="72"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2011,20 +2016,20 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="66" t="s">
+      <c r="Q6" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="68"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="70"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="71" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2036,7 +2041,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="71">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2072,11 +2077,11 @@
       <c r="Y7"/>
       <c r="AD7"/>
     </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="62"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -2086,7 +2091,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="62"/>
+      <c r="H8" s="64"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -2120,11 +2125,11 @@
       <c r="Y8"/>
       <c r="AD8"/>
     </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="64"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2134,7 +2139,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="62"/>
+      <c r="H9" s="64"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2160,11 +2165,11 @@
       <c r="Y9"/>
       <c r="AD9"/>
     </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="63"/>
+      <c r="C10" s="65"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2174,7 +2179,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="62"/>
+      <c r="H10" s="64"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2200,11 +2205,11 @@
       <c r="Y10"/>
       <c r="AD10"/>
     </row>
-    <row r="11" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:30" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="60">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2216,7 +2221,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="62"/>
+      <c r="H11" s="64"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2247,11 +2252,11 @@
       <c r="Y11"/>
       <c r="AD11"/>
     </row>
-    <row r="12" spans="2:30" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:30" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="61"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2261,7 +2266,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="63"/>
+      <c r="H12" s="65"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2283,11 +2288,11 @@
       <c r="Y12"/>
       <c r="AD12"/>
     </row>
-    <row r="13" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:30" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="59"/>
+      <c r="C13" s="61"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2297,7 +2302,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="60">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2318,10 +2323,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="71" t="s">
+      <c r="Q13" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="72"/>
+      <c r="R13" s="74"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2331,11 +2336,11 @@
       <c r="Y13"/>
       <c r="AD13"/>
     </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="59"/>
+      <c r="C14" s="61"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2345,14 +2350,13 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="59"/>
+      <c r="H14" s="61"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
       <c r="J14" s="32">
         <v>5</v>
       </c>
-      <c r="K14" s="51"/>
       <c r="L14" s="3">
         <v>82</v>
       </c>
@@ -2365,23 +2369,23 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="73" t="s">
+      <c r="Q14" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="74"/>
+      <c r="R14" s="76"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
       <c r="AD14"/>
     </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="59"/>
+      <c r="C15" s="61"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2391,7 +2395,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="62"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2401,13 +2405,19 @@
       <c r="L15" s="3">
         <v>83</v>
       </c>
-      <c r="M15" s="78"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="32"/>
-      <c r="Q15" s="73" t="s">
+      <c r="M15" s="52">
+        <v>46133</v>
+      </c>
+      <c r="N15" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="O15" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="74"/>
+      <c r="R15" s="76"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1000</v>
@@ -2416,11 +2426,11 @@
       <c r="Y15"/>
       <c r="AD15"/>
     </row>
-    <row r="16" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:30" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="60"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2430,7 +2440,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="58">
+      <c r="H16" s="60">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2442,16 +2452,22 @@
       <c r="L16" s="3">
         <v>84</v>
       </c>
-      <c r="M16" s="76"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="32"/>
-      <c r="Q16" s="64" t="s">
+      <c r="M16" s="52">
+        <v>46143</v>
+      </c>
+      <c r="N16" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="O16" s="32">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="65"/>
+      <c r="R16" s="67"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2459,11 +2475,11 @@
       <c r="Y16"/>
       <c r="AD16"/>
     </row>
-    <row r="17" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:30" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="60">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2475,7 +2491,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="59"/>
+      <c r="H17" s="61"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2485,17 +2501,17 @@
       <c r="L17" s="3">
         <v>85</v>
       </c>
-      <c r="M17" s="77"/>
+      <c r="M17" s="59"/>
       <c r="N17" s="34"/>
       <c r="O17" s="32"/>
       <c r="Y17"/>
       <c r="AD17"/>
     </row>
-    <row r="18" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="59"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2505,7 +2521,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="60"/>
+      <c r="H18" s="62"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2515,18 +2531,18 @@
       <c r="L18" s="3">
         <v>86</v>
       </c>
-      <c r="M18" s="78"/>
+      <c r="M18" s="51"/>
       <c r="N18" s="34"/>
       <c r="O18" s="32"/>
       <c r="S18" s="12"/>
       <c r="Y18"/>
       <c r="AD18"/>
     </row>
-    <row r="19" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="59"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2536,7 +2552,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="60">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2548,17 +2564,17 @@
       <c r="L19" s="3">
         <v>87</v>
       </c>
-      <c r="M19" s="76"/>
+      <c r="M19" s="58"/>
       <c r="N19" s="34"/>
       <c r="O19" s="32"/>
       <c r="Y19"/>
       <c r="AD19"/>
     </row>
-    <row r="20" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="59"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2568,7 +2584,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="59"/>
+      <c r="H20" s="61"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2578,17 +2594,17 @@
       <c r="L20" s="3">
         <v>88</v>
       </c>
-      <c r="M20" s="77"/>
+      <c r="M20" s="59"/>
       <c r="N20" s="35"/>
       <c r="O20" s="32"/>
       <c r="Y20"/>
       <c r="AD20"/>
     </row>
-    <row r="21" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="60"/>
+      <c r="C21" s="62"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2598,7 +2614,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="60"/>
+      <c r="H21" s="62"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2608,17 +2624,17 @@
       <c r="L21" s="3">
         <v>89</v>
       </c>
-      <c r="M21" s="78"/>
+      <c r="M21" s="51"/>
       <c r="N21" s="35"/>
       <c r="O21" s="32"/>
       <c r="Y21"/>
       <c r="AD21"/>
     </row>
-    <row r="22" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="60">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2648,11 +2664,11 @@
       <c r="Y22"/>
       <c r="AD22"/>
     </row>
-    <row r="23" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="59"/>
+      <c r="C23" s="61"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2681,11 +2697,11 @@
       <c r="Y23"/>
       <c r="AD23"/>
     </row>
-    <row r="24" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="59"/>
+      <c r="C24" s="61"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2713,11 +2729,11 @@
       <c r="Y24"/>
       <c r="AD24"/>
     </row>
-    <row r="25" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="59"/>
+      <c r="C25" s="61"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2745,11 +2761,11 @@
       <c r="Y25"/>
       <c r="AD25"/>
     </row>
-    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="59"/>
+      <c r="C26" s="61"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2759,7 +2775,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="58">
+      <c r="H26" s="60">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2771,17 +2787,17 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="58"/>
+      <c r="M26" s="60"/>
       <c r="N26" s="34"/>
       <c r="O26" s="32"/>
       <c r="Y26"/>
       <c r="AD26"/>
     </row>
-    <row r="27" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="60"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2791,7 +2807,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="59"/>
+      <c r="H27" s="61"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2801,13 +2817,13 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="59"/>
+      <c r="M27" s="61"/>
       <c r="N27" s="34"/>
       <c r="O27" s="36"/>
       <c r="Y27"/>
       <c r="AD27"/>
     </row>
-    <row r="28" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <v>22</v>
       </c>
@@ -2841,11 +2857,11 @@
       <c r="Y28"/>
       <c r="AD28"/>
     </row>
-    <row r="29" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="61">
+      <c r="C29" s="63">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2875,11 +2891,11 @@
       <c r="Y29"/>
       <c r="AD29"/>
     </row>
-    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="62"/>
+      <c r="C30" s="64"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2907,11 +2923,11 @@
       <c r="Y30"/>
       <c r="AD30"/>
     </row>
-    <row r="31" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="62"/>
+      <c r="C31" s="64"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2939,11 +2955,11 @@
       <c r="Y31"/>
       <c r="AD31"/>
     </row>
-    <row r="32" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="62"/>
+      <c r="C32" s="64"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2971,11 +2987,11 @@
       <c r="Y32"/>
       <c r="AD32"/>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="62"/>
+      <c r="C33" s="64"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -2985,7 +3001,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="61">
+      <c r="H33" s="63">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -2997,17 +3013,17 @@
       <c r="L33" s="3">
         <v>101</v>
       </c>
-      <c r="M33" s="61"/>
+      <c r="M33" s="63"/>
       <c r="N33" s="34"/>
       <c r="O33" s="36"/>
       <c r="Y33"/>
       <c r="AD33"/>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="62"/>
+      <c r="C34" s="64"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -3017,7 +3033,7 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="62"/>
+      <c r="H34" s="64"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
@@ -3027,17 +3043,17 @@
       <c r="L34" s="3">
         <v>102</v>
       </c>
-      <c r="M34" s="62"/>
+      <c r="M34" s="64"/>
       <c r="N34" s="37"/>
       <c r="O34" s="36"/>
       <c r="Y34"/>
       <c r="AD34"/>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="63"/>
+      <c r="C35" s="65"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -3048,7 +3064,7 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="62"/>
+      <c r="H35" s="64"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
@@ -3058,17 +3074,17 @@
       <c r="L35" s="3">
         <v>103</v>
       </c>
-      <c r="M35" s="62"/>
+      <c r="M35" s="64"/>
       <c r="N35" s="37"/>
       <c r="O35" s="36"/>
       <c r="Y35"/>
       <c r="AD35"/>
     </row>
-    <row r="36" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:30" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="61">
+      <c r="C36" s="63">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3080,7 +3096,7 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="62"/>
+      <c r="H36" s="64"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
@@ -3090,17 +3106,17 @@
       <c r="L36" s="3">
         <v>104</v>
       </c>
-      <c r="M36" s="62"/>
+      <c r="M36" s="64"/>
       <c r="N36" s="37"/>
       <c r="O36" s="36"/>
       <c r="Y36"/>
       <c r="AD36"/>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="62"/>
+      <c r="C37" s="64"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -3128,11 +3144,11 @@
       <c r="Y37"/>
       <c r="AD37"/>
     </row>
-    <row r="38" spans="2:30" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="62"/>
+      <c r="C38" s="64"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -3163,11 +3179,11 @@
       <c r="Y38"/>
       <c r="AD38"/>
     </row>
-    <row r="39" spans="2:30" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="62"/>
+      <c r="C39" s="64"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -3199,11 +3215,11 @@
       <c r="Y39"/>
       <c r="AD39"/>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="62"/>
+      <c r="C40" s="64"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -3234,11 +3250,11 @@
       <c r="Y40"/>
       <c r="AD40"/>
     </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="63"/>
+      <c r="C41" s="65"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -3269,11 +3285,11 @@
       <c r="Y41"/>
       <c r="AD41"/>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="61">
+      <c r="C42" s="63">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3306,11 +3322,11 @@
       <c r="Y42"/>
       <c r="AD42"/>
     </row>
-    <row r="43" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:30" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="62"/>
+      <c r="C43" s="64"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -3341,7 +3357,7 @@
       <c r="Y43"/>
       <c r="AD43"/>
     </row>
-    <row r="44" spans="2:30" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:30" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="20"/>
       <c r="C44" s="38" t="s">
         <v>69</v>
@@ -3368,7 +3384,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F54B860-3A80-4FB0-BB81-053D8DF48806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3438F689-9EB6-4B92-AFA6-CF58230F80EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="104">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -472,6 +461,10 @@
   </si>
   <si>
     <t>이원석</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>임봉석</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1512,30 +1505,6 @@
     <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1548,6 +1517,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1564,6 +1548,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1591,9 +1584,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1631,7 +1624,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1737,7 +1730,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1879,7 +1872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1931,52 +1924,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2016,12 +2009,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="68" t="s">
+      <c r="Q6" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
+      <c r="R6" s="61"/>
+      <c r="S6" s="61"/>
+      <c r="T6" s="62"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2029,7 +2022,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2041,7 +2034,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="71">
+      <c r="H7" s="63">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2209,7 +2202,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="60">
+      <c r="C11" s="66">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2256,7 +2249,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="61"/>
+      <c r="C12" s="67"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2292,7 +2285,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="61"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2302,7 +2295,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="60">
+      <c r="H13" s="66">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2323,10 +2316,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="73" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="74"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2340,7 +2333,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="61"/>
+      <c r="C14" s="67"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2350,7 +2343,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="61"/>
+      <c r="H14" s="67"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2369,13 +2362,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="75" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="76"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2385,7 +2378,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="61"/>
+      <c r="C15" s="67"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2395,7 +2388,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="62"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2414,10 +2407,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="75" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="76"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1000</v>
@@ -2430,7 +2423,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="62"/>
+      <c r="C16" s="68"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2440,7 +2433,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="60">
+      <c r="H16" s="66">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2461,13 +2454,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="66" t="s">
+      <c r="Q16" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="67"/>
+      <c r="R16" s="77"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1422</v>
+        <v>1427</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2479,7 +2472,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="66">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2491,7 +2484,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="61"/>
+      <c r="H17" s="67"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2501,9 +2494,15 @@
       <c r="L17" s="3">
         <v>85</v>
       </c>
-      <c r="M17" s="59"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="32"/>
+      <c r="M17" s="52">
+        <v>46148</v>
+      </c>
+      <c r="N17" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="O17" s="32">
+        <v>5</v>
+      </c>
       <c r="Y17"/>
       <c r="AD17"/>
     </row>
@@ -2511,7 +2510,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="61"/>
+      <c r="C18" s="67"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2521,7 +2520,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="62"/>
+      <c r="H18" s="68"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2542,7 +2541,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="61"/>
+      <c r="C19" s="67"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2552,7 +2551,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="60">
+      <c r="H19" s="66">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2567,6 +2566,9 @@
       <c r="M19" s="58"/>
       <c r="N19" s="34"/>
       <c r="O19" s="32"/>
+      <c r="Q19" s="1">
+        <v>46148</v>
+      </c>
       <c r="Y19"/>
       <c r="AD19"/>
     </row>
@@ -2574,7 +2576,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="61"/>
+      <c r="C20" s="67"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2584,7 +2586,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="61"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2604,7 +2606,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="62"/>
+      <c r="C21" s="68"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2614,7 +2616,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="62"/>
+      <c r="H21" s="68"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2634,7 +2636,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="60">
+      <c r="C22" s="66">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2668,7 +2670,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="61"/>
+      <c r="C23" s="67"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2701,7 +2703,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="61"/>
+      <c r="C24" s="67"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2733,7 +2735,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="61"/>
+      <c r="C25" s="67"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2765,7 +2767,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="61"/>
+      <c r="C26" s="67"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2775,7 +2777,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="60">
+      <c r="H26" s="66">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2787,7 +2789,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="60"/>
+      <c r="M26" s="66"/>
       <c r="N26" s="34"/>
       <c r="O26" s="32"/>
       <c r="Y26"/>
@@ -2797,7 +2799,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="62"/>
+      <c r="C27" s="68"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2807,7 +2809,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="61"/>
+      <c r="H27" s="67"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2817,7 +2819,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="61"/>
+      <c r="M27" s="67"/>
       <c r="N27" s="34"/>
       <c r="O27" s="36"/>
       <c r="Y27"/>
@@ -2861,7 +2863,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="63">
+      <c r="C29" s="75">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3001,7 +3003,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="63">
+      <c r="H33" s="75">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3013,7 +3015,7 @@
       <c r="L33" s="3">
         <v>101</v>
       </c>
-      <c r="M33" s="63"/>
+      <c r="M33" s="75"/>
       <c r="N33" s="34"/>
       <c r="O33" s="36"/>
       <c r="Y33"/>
@@ -3084,7 +3086,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="63">
+      <c r="C36" s="75">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3289,7 +3291,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="63">
+      <c r="C42" s="75">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3384,7 +3386,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3394,6 +3396,16 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="M33:M36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3406,16 +3418,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="M33:M36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3438F689-9EB6-4B92-AFA6-CF58230F80EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B158823-397F-4FD2-AF1F-4CD49A9AF0D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="105">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -465,6 +465,10 @@
   </si>
   <si>
     <t>임봉석</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>남무호</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1326,7 +1330,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1499,11 +1503,29 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1517,21 +1539,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1548,15 +1555,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1924,52 +1922,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2009,12 +2007,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="60" t="s">
+      <c r="Q6" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="61"/>
-      <c r="S6" s="61"/>
-      <c r="T6" s="62"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="68"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2022,7 +2020,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="69" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2034,7 +2032,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="63">
+      <c r="H7" s="69">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2074,7 +2072,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="64"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -2084,7 +2082,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="64"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -2122,7 +2120,7 @@
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="64"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2132,7 +2130,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="64"/>
+      <c r="H9" s="62"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2151,10 +2149,18 @@
       <c r="O9" s="32">
         <v>5</v>
       </c>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="45"/>
+      <c r="Q9" s="46">
+        <v>46169</v>
+      </c>
+      <c r="R9" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="S9" s="44">
+        <v>100</v>
+      </c>
+      <c r="T9" s="45" t="s">
+        <v>11</v>
+      </c>
       <c r="Y9"/>
       <c r="AD9"/>
     </row>
@@ -2162,7 +2168,7 @@
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="65"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2172,7 +2178,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="64"/>
+      <c r="H10" s="62"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2202,7 +2208,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="66">
+      <c r="C11" s="58">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2214,7 +2220,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="64"/>
+      <c r="H11" s="62"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2239,7 +2245,7 @@
       </c>
       <c r="S11" s="29">
         <f>SUM(S7:S10)</f>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="T11" s="11"/>
       <c r="Y11"/>
@@ -2249,7 +2255,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="67"/>
+      <c r="C12" s="59"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2259,7 +2265,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="65"/>
+      <c r="H12" s="63"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2285,7 +2291,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="67"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2295,7 +2301,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="58">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2316,10 +2322,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71"/>
+      <c r="R13" s="72"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2333,7 +2339,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="67"/>
+      <c r="C14" s="59"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2343,7 +2349,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="67"/>
+      <c r="H14" s="59"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2362,10 +2368,10 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="72" t="s">
+      <c r="Q14" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="73"/>
+      <c r="R14" s="74"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
         <v>427</v>
@@ -2378,7 +2384,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="67"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2388,7 +2394,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="68"/>
+      <c r="H15" s="60"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2407,13 +2413,13 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="73"/>
+      <c r="R15" s="74"/>
       <c r="S15" s="26">
         <f>S11</f>
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="T15" s="16"/>
       <c r="Y15"/>
@@ -2423,7 +2429,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="68"/>
+      <c r="C16" s="60"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2433,7 +2439,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="66">
+      <c r="H16" s="58">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2454,13 +2460,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="76" t="s">
+      <c r="Q16" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="77"/>
+      <c r="R16" s="65"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1427</v>
+        <v>1527</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2472,7 +2478,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="66">
+      <c r="C17" s="58">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2484,7 +2490,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="67"/>
+      <c r="H17" s="59"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2510,7 +2516,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="67"/>
+      <c r="C18" s="59"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2520,7 +2526,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="68"/>
+      <c r="H18" s="60"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2541,7 +2547,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="67"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2551,7 +2557,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="66">
+      <c r="H19" s="58">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2563,7 +2569,7 @@
       <c r="L19" s="3">
         <v>87</v>
       </c>
-      <c r="M19" s="58"/>
+      <c r="M19" s="54"/>
       <c r="N19" s="34"/>
       <c r="O19" s="32"/>
       <c r="Q19" s="1">
@@ -2576,7 +2582,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="67"/>
+      <c r="C20" s="59"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2586,7 +2592,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="67"/>
+      <c r="H20" s="59"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2596,7 +2602,7 @@
       <c r="L20" s="3">
         <v>88</v>
       </c>
-      <c r="M20" s="59"/>
+      <c r="M20" s="54"/>
       <c r="N20" s="35"/>
       <c r="O20" s="32"/>
       <c r="Y20"/>
@@ -2606,7 +2612,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="68"/>
+      <c r="C21" s="60"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2616,7 +2622,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="68"/>
+      <c r="H21" s="60"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2626,7 +2632,7 @@
       <c r="L21" s="3">
         <v>89</v>
       </c>
-      <c r="M21" s="51"/>
+      <c r="M21" s="54"/>
       <c r="N21" s="35"/>
       <c r="O21" s="32"/>
       <c r="Y21"/>
@@ -2636,7 +2642,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="66">
+      <c r="C22" s="58">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2670,7 +2676,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2703,7 +2709,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="67"/>
+      <c r="C24" s="59"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2735,7 +2741,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="67"/>
+      <c r="C25" s="59"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2767,7 +2773,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="67"/>
+      <c r="C26" s="59"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2777,7 +2783,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="66">
+      <c r="H26" s="58">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2789,7 +2795,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="66"/>
+      <c r="M26" s="54"/>
       <c r="N26" s="34"/>
       <c r="O26" s="32"/>
       <c r="Y26"/>
@@ -2799,7 +2805,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="68"/>
+      <c r="C27" s="60"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2809,7 +2815,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="67"/>
+      <c r="H27" s="59"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2819,7 +2825,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="67"/>
+      <c r="M27" s="54"/>
       <c r="N27" s="34"/>
       <c r="O27" s="36"/>
       <c r="Y27"/>
@@ -2853,7 +2859,7 @@
       <c r="L28" s="3">
         <v>96</v>
       </c>
-      <c r="M28" s="52"/>
+      <c r="M28" s="54"/>
       <c r="N28" s="34"/>
       <c r="O28" s="36"/>
       <c r="Y28"/>
@@ -2863,7 +2869,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="75">
+      <c r="C29" s="61">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2887,7 +2893,7 @@
       <c r="L29" s="3">
         <v>97</v>
       </c>
-      <c r="M29" s="52"/>
+      <c r="M29" s="54"/>
       <c r="N29" s="37"/>
       <c r="O29" s="36"/>
       <c r="Y29"/>
@@ -2897,7 +2903,7 @@
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="64"/>
+      <c r="C30" s="62"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2919,7 +2925,7 @@
       <c r="L30" s="3">
         <v>98</v>
       </c>
-      <c r="M30" s="52"/>
+      <c r="M30" s="54"/>
       <c r="N30" s="37"/>
       <c r="O30" s="36"/>
       <c r="Y30"/>
@@ -2929,7 +2935,7 @@
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="64"/>
+      <c r="C31" s="62"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2951,7 +2957,7 @@
       <c r="L31" s="3">
         <v>99</v>
       </c>
-      <c r="M31" s="52"/>
+      <c r="M31" s="54"/>
       <c r="N31" s="37"/>
       <c r="O31" s="36"/>
       <c r="Y31"/>
@@ -2961,7 +2967,7 @@
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="64"/>
+      <c r="C32" s="62"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2983,7 +2989,7 @@
       <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="52"/>
+      <c r="M32" s="54"/>
       <c r="N32" s="37"/>
       <c r="O32" s="36"/>
       <c r="Y32"/>
@@ -2993,7 +2999,7 @@
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="64"/>
+      <c r="C33" s="62"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -3003,7 +3009,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="75">
+      <c r="H33" s="61">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3015,7 +3021,7 @@
       <c r="L33" s="3">
         <v>101</v>
       </c>
-      <c r="M33" s="75"/>
+      <c r="M33" s="54"/>
       <c r="N33" s="34"/>
       <c r="O33" s="36"/>
       <c r="Y33"/>
@@ -3025,7 +3031,7 @@
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="64"/>
+      <c r="C34" s="62"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -3035,7 +3041,7 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="64"/>
+      <c r="H34" s="62"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
@@ -3045,7 +3051,7 @@
       <c r="L34" s="3">
         <v>102</v>
       </c>
-      <c r="M34" s="64"/>
+      <c r="M34" s="54"/>
       <c r="N34" s="37"/>
       <c r="O34" s="36"/>
       <c r="Y34"/>
@@ -3055,7 +3061,7 @@
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="65"/>
+      <c r="C35" s="63"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -3066,7 +3072,7 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="64"/>
+      <c r="H35" s="62"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
@@ -3076,7 +3082,7 @@
       <c r="L35" s="3">
         <v>103</v>
       </c>
-      <c r="M35" s="64"/>
+      <c r="M35" s="54"/>
       <c r="N35" s="37"/>
       <c r="O35" s="36"/>
       <c r="Y35"/>
@@ -3086,7 +3092,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="75">
+      <c r="C36" s="61">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3098,7 +3104,7 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="64"/>
+      <c r="H36" s="62"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
@@ -3108,7 +3114,7 @@
       <c r="L36" s="3">
         <v>104</v>
       </c>
-      <c r="M36" s="64"/>
+      <c r="M36" s="54"/>
       <c r="N36" s="37"/>
       <c r="O36" s="36"/>
       <c r="Y36"/>
@@ -3118,7 +3124,7 @@
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="64"/>
+      <c r="C37" s="62"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -3150,7 +3156,7 @@
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="64"/>
+      <c r="C38" s="62"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -3185,7 +3191,7 @@
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="64"/>
+      <c r="C39" s="62"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -3221,7 +3227,7 @@
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="64"/>
+      <c r="C40" s="62"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -3256,7 +3262,7 @@
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="65"/>
+      <c r="C41" s="63"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -3291,7 +3297,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="75">
+      <c r="C42" s="61">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3328,7 +3334,7 @@
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="64"/>
+      <c r="C43" s="62"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -3395,17 +3401,7 @@
     </row>
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="M26:M27"/>
-    <mergeCell ref="M33:M36"/>
+  <mergeCells count="20">
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3418,6 +3414,14 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B158823-397F-4FD2-AF1F-4CD49A9AF0D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C5E594-5EAF-4D5C-8673-5C785542D4F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="106">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -469,6 +469,10 @@
   </si>
   <si>
     <t>남무호</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별회비</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1503,30 +1507,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1539,6 +1519,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1555,6 +1550,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1922,52 +1926,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72"/>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2007,12 +2011,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="66" t="s">
+      <c r="Q6" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="67"/>
-      <c r="S6" s="67"/>
-      <c r="T6" s="68"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="60"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2020,7 +2024,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="61" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2032,7 +2036,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="61">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2159,7 +2163,7 @@
         <v>100</v>
       </c>
       <c r="T9" s="45" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="Y9"/>
       <c r="AD9"/>
@@ -2208,7 +2212,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="64">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2255,7 +2259,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="59"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2291,7 +2295,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="59"/>
+      <c r="C13" s="65"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2301,7 +2305,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="64">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2322,10 +2326,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="71" t="s">
+      <c r="Q13" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="72"/>
+      <c r="R13" s="69"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2339,7 +2343,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="59"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2349,7 +2353,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="59"/>
+      <c r="H14" s="65"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2368,10 +2372,10 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="73" t="s">
+      <c r="Q14" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="74"/>
+      <c r="R14" s="71"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
         <v>427</v>
@@ -2384,7 +2388,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="59"/>
+      <c r="C15" s="65"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2394,7 +2398,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="60"/>
+      <c r="H15" s="66"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2413,10 +2417,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="73" t="s">
+      <c r="Q15" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="74"/>
+      <c r="R15" s="71"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2429,7 +2433,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="60"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2439,7 +2443,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="58">
+      <c r="H16" s="64">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2460,10 +2464,10 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="64" t="s">
+      <c r="Q16" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="65"/>
+      <c r="R16" s="75"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
         <v>1527</v>
@@ -2478,7 +2482,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="58">
+      <c r="C17" s="64">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2490,7 +2494,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="59"/>
+      <c r="H17" s="65"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2516,7 +2520,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="59"/>
+      <c r="C18" s="65"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2526,7 +2530,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="60"/>
+      <c r="H18" s="66"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2547,7 +2551,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="59"/>
+      <c r="C19" s="65"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2557,7 +2561,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="64">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2582,7 +2586,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="59"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2592,7 +2596,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="59"/>
+      <c r="H20" s="65"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2612,7 +2616,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="60"/>
+      <c r="C21" s="66"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2622,7 +2626,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="60"/>
+      <c r="H21" s="66"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2642,7 +2646,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="64">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2676,7 +2680,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="59"/>
+      <c r="C23" s="65"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2709,7 +2713,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="59"/>
+      <c r="C24" s="65"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2741,7 +2745,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="59"/>
+      <c r="C25" s="65"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2773,7 +2777,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="59"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2783,7 +2787,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="58">
+      <c r="H26" s="64">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2805,7 +2809,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="60"/>
+      <c r="C27" s="66"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2815,7 +2819,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="59"/>
+      <c r="H27" s="65"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2869,7 +2873,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="61">
+      <c r="C29" s="73">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3009,7 +3013,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="61">
+      <c r="H33" s="73">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3092,7 +3096,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="61">
+      <c r="C36" s="73">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3297,7 +3301,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="61">
+      <c r="C42" s="73">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3402,6 +3406,14 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3414,14 +3426,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C5E594-5EAF-4D5C-8673-5C785542D4F3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EC124E-FC4F-4722-95C8-E68619120F02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -473,6 +473,14 @@
   </si>
   <si>
     <t>특별회비</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>임승빈</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이인길</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1334,7 +1342,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1486,9 +1494,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1505,6 +1510,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1519,21 +1548,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1550,15 +1564,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1926,52 +1931,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2011,12 +2016,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="58" t="s">
+      <c r="Q6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="59"/>
-      <c r="S6" s="59"/>
-      <c r="T6" s="60"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2024,7 +2029,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2036,7 +2041,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="61">
+      <c r="H7" s="68">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2048,7 +2053,7 @@
       <c r="L7" s="3">
         <v>75</v>
       </c>
-      <c r="M7" s="57">
+      <c r="M7" s="56">
         <v>46108</v>
       </c>
       <c r="N7" s="31" t="s">
@@ -2076,7 +2081,7 @@
       <c r="B8" s="4">
         <v>2</v>
       </c>
-      <c r="C8" s="62"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="31" t="s">
         <v>18</v>
       </c>
@@ -2086,7 +2091,7 @@
       <c r="G8" s="3">
         <v>39</v>
       </c>
-      <c r="H8" s="62"/>
+      <c r="H8" s="61"/>
       <c r="I8" s="31" t="s">
         <v>55</v>
       </c>
@@ -2096,7 +2101,7 @@
       <c r="L8" s="3">
         <v>76</v>
       </c>
-      <c r="M8" s="52">
+      <c r="M8" s="51">
         <v>46109</v>
       </c>
       <c r="N8" s="31" t="s">
@@ -2124,7 +2129,7 @@
       <c r="B9" s="3">
         <v>3</v>
       </c>
-      <c r="C9" s="62"/>
+      <c r="C9" s="61"/>
       <c r="D9" s="33" t="s">
         <v>12</v>
       </c>
@@ -2134,7 +2139,7 @@
       <c r="G9" s="3">
         <v>40</v>
       </c>
-      <c r="H9" s="62"/>
+      <c r="H9" s="61"/>
       <c r="I9" s="33" t="s">
         <v>56</v>
       </c>
@@ -2144,7 +2149,7 @@
       <c r="L9" s="3">
         <v>77</v>
       </c>
-      <c r="M9" s="52">
+      <c r="M9" s="51">
         <v>46111</v>
       </c>
       <c r="N9" s="33" t="s">
@@ -2172,7 +2177,7 @@
       <c r="B10" s="3">
         <v>4</v>
       </c>
-      <c r="C10" s="63"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="34" t="s">
         <v>19</v>
       </c>
@@ -2182,7 +2187,7 @@
       <c r="G10" s="3">
         <v>41</v>
       </c>
-      <c r="H10" s="62"/>
+      <c r="H10" s="61"/>
       <c r="I10" s="34" t="s">
         <v>57</v>
       </c>
@@ -2192,7 +2197,7 @@
       <c r="L10" s="3">
         <v>78</v>
       </c>
-      <c r="M10" s="52">
+      <c r="M10" s="51">
         <v>46116</v>
       </c>
       <c r="N10" s="34" t="s">
@@ -2212,7 +2217,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="64">
+      <c r="C11" s="57">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2224,7 +2229,7 @@
       <c r="G11" s="3">
         <v>42</v>
       </c>
-      <c r="H11" s="62"/>
+      <c r="H11" s="61"/>
       <c r="I11" s="34" t="s">
         <v>58</v>
       </c>
@@ -2234,7 +2239,7 @@
       <c r="L11" s="3">
         <v>79</v>
       </c>
-      <c r="M11" s="52">
+      <c r="M11" s="51">
         <v>46117</v>
       </c>
       <c r="N11" s="34" t="s">
@@ -2259,7 +2264,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="65"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2269,7 +2274,7 @@
       <c r="G12" s="3">
         <v>43</v>
       </c>
-      <c r="H12" s="63"/>
+      <c r="H12" s="62"/>
       <c r="I12" s="34" t="s">
         <v>59</v>
       </c>
@@ -2279,7 +2284,7 @@
       <c r="L12" s="3">
         <v>80</v>
       </c>
-      <c r="M12" s="52">
+      <c r="M12" s="51">
         <v>46123</v>
       </c>
       <c r="N12" s="34" t="s">
@@ -2295,7 +2300,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="65"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2305,7 +2310,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="64">
+      <c r="H13" s="57">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2317,7 +2322,7 @@
       <c r="L13" s="3">
         <v>81</v>
       </c>
-      <c r="M13" s="52">
+      <c r="M13" s="51">
         <v>46125</v>
       </c>
       <c r="N13" s="34" t="s">
@@ -2326,10 +2331,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="68" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="69"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2343,7 +2348,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="65"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2353,7 +2358,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="65"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2363,7 +2368,7 @@
       <c r="L14" s="3">
         <v>82</v>
       </c>
-      <c r="M14" s="52">
+      <c r="M14" s="51">
         <v>46127</v>
       </c>
       <c r="N14" s="34" t="s">
@@ -2372,13 +2377,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="70" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="71"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2388,7 +2393,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="65"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2398,7 +2403,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="66"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2408,7 +2413,7 @@
       <c r="L15" s="3">
         <v>83</v>
       </c>
-      <c r="M15" s="52">
+      <c r="M15" s="51">
         <v>46133</v>
       </c>
       <c r="N15" s="34" t="s">
@@ -2417,10 +2422,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="70" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="71"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2433,7 +2438,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="66"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2443,7 +2448,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="64">
+      <c r="H16" s="57">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2455,7 +2460,7 @@
       <c r="L16" s="3">
         <v>84</v>
       </c>
-      <c r="M16" s="52">
+      <c r="M16" s="51">
         <v>46143</v>
       </c>
       <c r="N16" s="34" t="s">
@@ -2464,13 +2469,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="74" t="s">
+      <c r="Q16" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="75"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1527</v>
+        <v>1537</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2482,7 +2487,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="64">
+      <c r="C17" s="57">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2494,7 +2499,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="65"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2504,7 +2509,7 @@
       <c r="L17" s="3">
         <v>85</v>
       </c>
-      <c r="M17" s="52">
+      <c r="M17" s="51">
         <v>46148</v>
       </c>
       <c r="N17" s="34" t="s">
@@ -2520,7 +2525,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="65"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2530,7 +2535,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="66"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2540,9 +2545,15 @@
       <c r="L18" s="3">
         <v>86</v>
       </c>
-      <c r="M18" s="51"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="32"/>
+      <c r="M18" s="51">
+        <v>46161</v>
+      </c>
+      <c r="N18" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="O18" s="32">
+        <v>5</v>
+      </c>
       <c r="S18" s="12"/>
       <c r="Y18"/>
       <c r="AD18"/>
@@ -2551,7 +2562,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="65"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2561,7 +2572,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="64">
+      <c r="H19" s="57">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2573,9 +2584,15 @@
       <c r="L19" s="3">
         <v>87</v>
       </c>
-      <c r="M19" s="54"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="32"/>
+      <c r="M19" s="53">
+        <v>46178</v>
+      </c>
+      <c r="N19" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="O19" s="32">
+        <v>5</v>
+      </c>
       <c r="Q19" s="1">
         <v>46148</v>
       </c>
@@ -2586,7 +2603,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="65"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2596,7 +2613,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="65"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2606,7 +2623,7 @@
       <c r="L20" s="3">
         <v>88</v>
       </c>
-      <c r="M20" s="54"/>
+      <c r="M20" s="53"/>
       <c r="N20" s="35"/>
       <c r="O20" s="32"/>
       <c r="Y20"/>
@@ -2616,7 +2633,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="66"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2626,7 +2643,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="66"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2636,7 +2653,7 @@
       <c r="L21" s="3">
         <v>89</v>
       </c>
-      <c r="M21" s="54"/>
+      <c r="M21" s="53"/>
       <c r="N21" s="35"/>
       <c r="O21" s="32"/>
       <c r="Y21"/>
@@ -2646,7 +2663,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="64">
+      <c r="C22" s="57">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2658,7 +2675,7 @@
       <c r="G22" s="3">
         <v>53</v>
       </c>
-      <c r="H22" s="54">
+      <c r="H22" s="53">
         <v>46043</v>
       </c>
       <c r="I22" s="35" t="s">
@@ -2670,7 +2687,7 @@
       <c r="L22" s="3">
         <v>90</v>
       </c>
-      <c r="M22" s="54"/>
+      <c r="M22" s="53"/>
       <c r="N22" s="35"/>
       <c r="O22" s="32"/>
       <c r="Y22"/>
@@ -2680,7 +2697,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2690,7 +2707,7 @@
       <c r="G23" s="3">
         <v>54</v>
       </c>
-      <c r="H23" s="54">
+      <c r="H23" s="53">
         <v>46045</v>
       </c>
       <c r="I23" s="35" t="s">
@@ -2702,7 +2719,7 @@
       <c r="L23" s="3">
         <v>91</v>
       </c>
-      <c r="M23" s="54"/>
+      <c r="M23" s="53"/>
       <c r="N23" s="35"/>
       <c r="O23" s="32"/>
       <c r="V23" s="7"/>
@@ -2713,7 +2730,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2723,7 +2740,7 @@
       <c r="G24" s="3">
         <v>55</v>
       </c>
-      <c r="H24" s="54">
+      <c r="H24" s="53">
         <v>46048</v>
       </c>
       <c r="I24" s="35" t="s">
@@ -2735,7 +2752,7 @@
       <c r="L24" s="3">
         <v>92</v>
       </c>
-      <c r="M24" s="54"/>
+      <c r="M24" s="53"/>
       <c r="N24" s="35"/>
       <c r="O24" s="32"/>
       <c r="Y24"/>
@@ -2745,7 +2762,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="65"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2755,7 +2772,7 @@
       <c r="G25" s="3">
         <v>56</v>
       </c>
-      <c r="H25" s="53">
+      <c r="H25" s="52">
         <v>46054</v>
       </c>
       <c r="I25" s="35" t="s">
@@ -2767,7 +2784,7 @@
       <c r="L25" s="3">
         <v>93</v>
       </c>
-      <c r="M25" s="53"/>
+      <c r="M25" s="52"/>
       <c r="N25" s="35"/>
       <c r="O25" s="32"/>
       <c r="Y25"/>
@@ -2777,7 +2794,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="65"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2787,7 +2804,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="64">
+      <c r="H26" s="57">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2799,7 +2816,7 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="54"/>
+      <c r="M26" s="53"/>
       <c r="N26" s="34"/>
       <c r="O26" s="32"/>
       <c r="Y26"/>
@@ -2809,7 +2826,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="66"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2819,7 +2836,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="65"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2829,7 +2846,7 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="54"/>
+      <c r="M27" s="53"/>
       <c r="N27" s="34"/>
       <c r="O27" s="36"/>
       <c r="Y27"/>
@@ -2839,7 +2856,7 @@
       <c r="B28" s="3">
         <v>22</v>
       </c>
-      <c r="C28" s="52">
+      <c r="C28" s="51">
         <v>46026</v>
       </c>
       <c r="D28" s="34" t="s">
@@ -2851,7 +2868,7 @@
       <c r="G28" s="3">
         <v>59</v>
       </c>
-      <c r="H28" s="52">
+      <c r="H28" s="51">
         <v>46059</v>
       </c>
       <c r="I28" s="34" t="s">
@@ -2863,7 +2880,7 @@
       <c r="L28" s="3">
         <v>96</v>
       </c>
-      <c r="M28" s="54"/>
+      <c r="M28" s="53"/>
       <c r="N28" s="34"/>
       <c r="O28" s="36"/>
       <c r="Y28"/>
@@ -2873,7 +2890,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="73">
+      <c r="C29" s="60">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -2885,7 +2902,7 @@
       <c r="G29" s="3">
         <v>60</v>
       </c>
-      <c r="H29" s="52">
+      <c r="H29" s="51">
         <v>46060</v>
       </c>
       <c r="I29" s="37" t="s">
@@ -2897,7 +2914,7 @@
       <c r="L29" s="3">
         <v>97</v>
       </c>
-      <c r="M29" s="54"/>
+      <c r="M29" s="53"/>
       <c r="N29" s="37"/>
       <c r="O29" s="36"/>
       <c r="Y29"/>
@@ -2907,7 +2924,7 @@
       <c r="B30" s="3">
         <v>24</v>
       </c>
-      <c r="C30" s="62"/>
+      <c r="C30" s="61"/>
       <c r="D30" s="37" t="s">
         <v>40</v>
       </c>
@@ -2917,7 +2934,7 @@
       <c r="G30" s="3">
         <v>61</v>
       </c>
-      <c r="H30" s="52">
+      <c r="H30" s="51">
         <v>46061</v>
       </c>
       <c r="I30" s="37" t="s">
@@ -2929,7 +2946,7 @@
       <c r="L30" s="3">
         <v>98</v>
       </c>
-      <c r="M30" s="54"/>
+      <c r="M30" s="53"/>
       <c r="N30" s="37"/>
       <c r="O30" s="36"/>
       <c r="Y30"/>
@@ -2939,7 +2956,7 @@
       <c r="B31" s="3">
         <v>25</v>
       </c>
-      <c r="C31" s="62"/>
+      <c r="C31" s="61"/>
       <c r="D31" s="37" t="s">
         <v>41</v>
       </c>
@@ -2949,7 +2966,7 @@
       <c r="G31" s="3">
         <v>62</v>
       </c>
-      <c r="H31" s="52">
+      <c r="H31" s="51">
         <v>46066</v>
       </c>
       <c r="I31" s="37" t="s">
@@ -2961,7 +2978,7 @@
       <c r="L31" s="3">
         <v>99</v>
       </c>
-      <c r="M31" s="54"/>
+      <c r="M31" s="53"/>
       <c r="N31" s="37"/>
       <c r="O31" s="36"/>
       <c r="Y31"/>
@@ -2971,7 +2988,7 @@
       <c r="B32" s="3">
         <v>26</v>
       </c>
-      <c r="C32" s="62"/>
+      <c r="C32" s="61"/>
       <c r="D32" s="37" t="s">
         <v>42</v>
       </c>
@@ -2981,7 +2998,7 @@
       <c r="G32" s="3">
         <v>63</v>
       </c>
-      <c r="H32" s="52">
+      <c r="H32" s="51">
         <v>46072</v>
       </c>
       <c r="I32" s="37" t="s">
@@ -2993,7 +3010,7 @@
       <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="54"/>
+      <c r="M32" s="53"/>
       <c r="N32" s="37"/>
       <c r="O32" s="36"/>
       <c r="Y32"/>
@@ -3003,7 +3020,7 @@
       <c r="B33" s="3">
         <v>27</v>
       </c>
-      <c r="C33" s="62"/>
+      <c r="C33" s="61"/>
       <c r="D33" s="34" t="s">
         <v>43</v>
       </c>
@@ -3013,7 +3030,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="73">
+      <c r="H33" s="60">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3025,7 +3042,7 @@
       <c r="L33" s="3">
         <v>101</v>
       </c>
-      <c r="M33" s="54"/>
+      <c r="M33" s="53"/>
       <c r="N33" s="34"/>
       <c r="O33" s="36"/>
       <c r="Y33"/>
@@ -3035,7 +3052,7 @@
       <c r="B34" s="3">
         <v>28</v>
       </c>
-      <c r="C34" s="62"/>
+      <c r="C34" s="61"/>
       <c r="D34" s="37" t="s">
         <v>44</v>
       </c>
@@ -3045,7 +3062,7 @@
       <c r="G34" s="3">
         <v>65</v>
       </c>
-      <c r="H34" s="62"/>
+      <c r="H34" s="61"/>
       <c r="I34" s="37" t="s">
         <v>83</v>
       </c>
@@ -3055,7 +3072,7 @@
       <c r="L34" s="3">
         <v>102</v>
       </c>
-      <c r="M34" s="54"/>
+      <c r="M34" s="53"/>
       <c r="N34" s="37"/>
       <c r="O34" s="36"/>
       <c r="Y34"/>
@@ -3065,7 +3082,7 @@
       <c r="B35" s="3">
         <v>29</v>
       </c>
-      <c r="C35" s="63"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="37" t="s">
         <v>45</v>
       </c>
@@ -3076,7 +3093,7 @@
       <c r="G35" s="3">
         <v>66</v>
       </c>
-      <c r="H35" s="62"/>
+      <c r="H35" s="61"/>
       <c r="I35" s="37" t="s">
         <v>84</v>
       </c>
@@ -3086,7 +3103,7 @@
       <c r="L35" s="3">
         <v>103</v>
       </c>
-      <c r="M35" s="54"/>
+      <c r="M35" s="53"/>
       <c r="N35" s="37"/>
       <c r="O35" s="36"/>
       <c r="Y35"/>
@@ -3096,7 +3113,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="73">
+      <c r="C36" s="60">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3108,7 +3125,7 @@
       <c r="G36" s="3">
         <v>67</v>
       </c>
-      <c r="H36" s="62"/>
+      <c r="H36" s="61"/>
       <c r="I36" s="37" t="s">
         <v>85</v>
       </c>
@@ -3118,7 +3135,7 @@
       <c r="L36" s="3">
         <v>104</v>
       </c>
-      <c r="M36" s="54"/>
+      <c r="M36" s="53"/>
       <c r="N36" s="37"/>
       <c r="O36" s="36"/>
       <c r="Y36"/>
@@ -3128,7 +3145,7 @@
       <c r="B37" s="3">
         <v>31</v>
       </c>
-      <c r="C37" s="62"/>
+      <c r="C37" s="61"/>
       <c r="D37" s="50" t="s">
         <v>47</v>
       </c>
@@ -3138,7 +3155,7 @@
       <c r="G37" s="3">
         <v>68</v>
       </c>
-      <c r="H37" s="52">
+      <c r="H37" s="51">
         <v>46078</v>
       </c>
       <c r="I37" s="50" t="s">
@@ -3150,7 +3167,7 @@
       <c r="L37" s="3">
         <v>105</v>
       </c>
-      <c r="M37" s="52"/>
+      <c r="M37" s="51"/>
       <c r="N37" s="50"/>
       <c r="O37" s="36"/>
       <c r="Y37"/>
@@ -3160,7 +3177,7 @@
       <c r="B38" s="3">
         <v>32</v>
       </c>
-      <c r="C38" s="62"/>
+      <c r="C38" s="61"/>
       <c r="D38" s="41" t="s">
         <v>48</v>
       </c>
@@ -3170,7 +3187,7 @@
       <c r="G38" s="3">
         <v>69</v>
       </c>
-      <c r="H38" s="52">
+      <c r="H38" s="51">
         <v>46081</v>
       </c>
       <c r="I38" s="41" t="s">
@@ -3183,7 +3200,7 @@
       <c r="L38" s="3">
         <v>106</v>
       </c>
-      <c r="M38" s="52"/>
+      <c r="M38" s="51"/>
       <c r="N38" s="41"/>
       <c r="O38" s="36"/>
       <c r="P38" s="2"/>
@@ -3195,7 +3212,7 @@
       <c r="B39" s="3">
         <v>33</v>
       </c>
-      <c r="C39" s="62"/>
+      <c r="C39" s="61"/>
       <c r="D39" s="41" t="s">
         <v>49</v>
       </c>
@@ -3206,7 +3223,7 @@
       <c r="G39" s="3">
         <v>70</v>
       </c>
-      <c r="H39" s="52">
+      <c r="H39" s="51">
         <v>46085</v>
       </c>
       <c r="I39" s="41" t="s">
@@ -3219,7 +3236,7 @@
       <c r="L39" s="3">
         <v>107</v>
       </c>
-      <c r="M39" s="52"/>
+      <c r="M39" s="51"/>
       <c r="N39" s="41"/>
       <c r="O39" s="36"/>
       <c r="P39" s="2"/>
@@ -3231,7 +3248,7 @@
       <c r="B40" s="3">
         <v>34</v>
       </c>
-      <c r="C40" s="62"/>
+      <c r="C40" s="61"/>
       <c r="D40" s="41" t="s">
         <v>50</v>
       </c>
@@ -3241,7 +3258,7 @@
       <c r="G40" s="3">
         <v>71</v>
       </c>
-      <c r="H40" s="52">
+      <c r="H40" s="51">
         <v>46089</v>
       </c>
       <c r="I40" s="41" t="s">
@@ -3254,7 +3271,7 @@
       <c r="L40" s="3">
         <v>108</v>
       </c>
-      <c r="M40" s="52"/>
+      <c r="M40" s="51"/>
       <c r="N40" s="41"/>
       <c r="O40" s="36"/>
       <c r="P40" s="2"/>
@@ -3266,7 +3283,7 @@
       <c r="B41" s="3">
         <v>35</v>
       </c>
-      <c r="C41" s="63"/>
+      <c r="C41" s="62"/>
       <c r="D41" s="41" t="s">
         <v>51</v>
       </c>
@@ -3276,7 +3293,7 @@
       <c r="G41" s="3">
         <v>72</v>
       </c>
-      <c r="H41" s="55">
+      <c r="H41" s="54">
         <v>46093</v>
       </c>
       <c r="I41" s="41" t="s">
@@ -3289,7 +3306,7 @@
       <c r="L41" s="3">
         <v>109</v>
       </c>
-      <c r="M41" s="55"/>
+      <c r="M41" s="54"/>
       <c r="N41" s="41"/>
       <c r="O41" s="36"/>
       <c r="P41" s="2"/>
@@ -3301,7 +3318,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="73">
+      <c r="C42" s="60">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3313,7 +3330,7 @@
       <c r="G42" s="3">
         <v>73</v>
       </c>
-      <c r="H42" s="52">
+      <c r="H42" s="51">
         <v>46097</v>
       </c>
       <c r="I42" s="35" t="s">
@@ -3326,7 +3343,7 @@
       <c r="L42" s="3">
         <v>110</v>
       </c>
-      <c r="M42" s="52"/>
+      <c r="M42" s="51"/>
       <c r="N42" s="35"/>
       <c r="O42" s="36"/>
       <c r="P42" s="2"/>
@@ -3338,7 +3355,7 @@
       <c r="B43" s="4">
         <v>37</v>
       </c>
-      <c r="C43" s="62"/>
+      <c r="C43" s="61"/>
       <c r="D43" s="35" t="s">
         <v>53</v>
       </c>
@@ -3348,7 +3365,7 @@
       <c r="G43" s="3">
         <v>74</v>
       </c>
-      <c r="H43" s="56">
+      <c r="H43" s="55">
         <v>46099</v>
       </c>
       <c r="I43" s="35" t="s">
@@ -3361,7 +3378,7 @@
       <c r="L43" s="3">
         <v>111</v>
       </c>
-      <c r="M43" s="56"/>
+      <c r="M43" s="55"/>
       <c r="N43" s="35"/>
       <c r="O43" s="36"/>
       <c r="P43" s="2"/>
@@ -3396,7 +3413,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3406,14 +3423,6 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3426,6 +3435,14 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shell\kang\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EC124E-FC4F-4722-95C8-E68619120F02}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B26C48-EB93-4178-8F87-474298C3FA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="111">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -481,6 +492,18 @@
   </si>
   <si>
     <t>이인길</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김희덕</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김종찬</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>박성근</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1512,30 +1535,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1548,6 +1547,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1564,6 +1578,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1591,9 +1614,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1631,7 +1654,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1737,7 +1760,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1879,7 +1902,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1931,52 +1954,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2016,12 +2039,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="59"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2029,7 +2052,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2041,7 +2064,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2217,7 +2240,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2264,7 +2287,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2300,7 +2323,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2310,7 +2333,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2331,10 +2354,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71"/>
+      <c r="R13" s="68"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2348,7 +2371,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2358,7 +2381,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2377,13 +2400,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="72" t="s">
+      <c r="Q14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="73"/>
+      <c r="R14" s="70"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2393,7 +2416,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2403,7 +2426,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="59"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2422,10 +2445,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="73"/>
+      <c r="R15" s="70"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2438,7 +2461,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="59"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2448,7 +2471,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2469,13 +2492,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="63" t="s">
+      <c r="Q16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="64"/>
+      <c r="R16" s="74"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1537</v>
+        <v>1552</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2487,7 +2510,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2499,7 +2522,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="58"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2525,7 +2548,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2535,7 +2558,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="59"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2562,7 +2585,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="58"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2572,7 +2595,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2603,7 +2626,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2613,7 +2636,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2623,9 +2646,15 @@
       <c r="L20" s="3">
         <v>88</v>
       </c>
-      <c r="M20" s="53"/>
-      <c r="N20" s="35"/>
-      <c r="O20" s="32"/>
+      <c r="M20" s="53">
+        <v>46206</v>
+      </c>
+      <c r="N20" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="O20" s="32">
+        <v>5</v>
+      </c>
       <c r="Y20"/>
       <c r="AD20"/>
     </row>
@@ -2633,7 +2662,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2643,7 +2672,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="59"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2653,9 +2682,15 @@
       <c r="L21" s="3">
         <v>89</v>
       </c>
-      <c r="M21" s="53"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="32"/>
+      <c r="M21" s="53">
+        <v>46209</v>
+      </c>
+      <c r="N21" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="O21" s="32">
+        <v>5</v>
+      </c>
       <c r="Y21"/>
       <c r="AD21"/>
     </row>
@@ -2663,7 +2698,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2687,9 +2722,15 @@
       <c r="L22" s="3">
         <v>90</v>
       </c>
-      <c r="M22" s="53"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="32"/>
+      <c r="M22" s="53">
+        <v>46210</v>
+      </c>
+      <c r="N22" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="O22" s="32">
+        <v>5</v>
+      </c>
       <c r="Y22"/>
       <c r="AD22"/>
     </row>
@@ -2697,7 +2738,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="58"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2730,7 +2771,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2762,7 +2803,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="58"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2794,7 +2835,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2804,7 +2845,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2826,7 +2867,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="59"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2836,7 +2877,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="58"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2890,7 +2931,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3030,7 +3071,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3113,7 +3154,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3318,7 +3359,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="60">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3413,7 +3454,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3423,6 +3464,14 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3435,14 +3484,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shell\kang\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B26C48-EB93-4178-8F87-474298C3FA21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0C9B41E-8BEC-436C-868F-BAA2F8AC34C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="113">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -504,6 +493,14 @@
   </si>
   <si>
     <t>박성근</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>이영진</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김용희</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1535,6 +1532,30 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1547,21 +1568,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1578,15 +1584,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1614,9 +1611,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1654,7 +1651,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1760,7 +1757,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1902,7 +1899,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1954,52 +1951,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2039,12 +2036,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="59"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2052,7 +2049,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2064,7 +2061,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="68">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2240,7 +2237,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="57">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2287,7 +2284,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2323,7 +2320,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2333,7 +2330,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="57">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2354,10 +2351,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="67" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="68"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2371,7 +2368,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2381,7 +2378,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2400,13 +2397,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="69" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="70"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2416,7 +2413,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2426,7 +2423,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2445,10 +2442,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="69" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="70"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2461,7 +2458,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2471,7 +2468,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="57">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2492,13 +2489,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="Q16" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="74"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2510,7 +2507,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="57">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2522,7 +2519,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2548,7 +2545,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2558,7 +2555,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2585,7 +2582,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2595,7 +2592,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="57">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2626,7 +2623,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2636,7 +2633,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2662,7 +2659,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2672,7 +2669,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2698,7 +2695,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="57">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2738,7 +2735,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2760,9 +2757,15 @@
       <c r="L23" s="3">
         <v>91</v>
       </c>
-      <c r="M23" s="53"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="32"/>
+      <c r="M23" s="53">
+        <v>46220</v>
+      </c>
+      <c r="N23" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23" s="32">
+        <v>5</v>
+      </c>
       <c r="V23" s="7"/>
       <c r="Y23"/>
       <c r="AD23"/>
@@ -2771,7 +2774,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2793,9 +2796,15 @@
       <c r="L24" s="3">
         <v>92</v>
       </c>
-      <c r="M24" s="53"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="32"/>
+      <c r="M24" s="53">
+        <v>46223</v>
+      </c>
+      <c r="N24" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="O24" s="32">
+        <v>5</v>
+      </c>
       <c r="Y24"/>
       <c r="AD24"/>
     </row>
@@ -2803,7 +2812,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2835,7 +2844,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2845,7 +2854,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="57">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2867,7 +2876,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2877,7 +2886,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2931,7 +2940,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="60">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3071,7 +3080,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="60">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3154,7 +3163,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="60">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3359,7 +3368,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="60">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3454,7 +3463,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3464,14 +3473,6 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3484,6 +3485,14 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0C9B41E-8BEC-436C-868F-BAA2F8AC34C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4595B3-11C7-44C8-8C62-EF56FCA679EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4595B3-11C7-44C8-8C62-EF56FCA679EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08551A1-2A14-45C2-80E0-90536F021B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="114">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -501,6 +501,10 @@
   </si>
   <si>
     <t>김용희</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>남무호</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1532,30 +1536,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1568,6 +1548,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1584,6 +1579,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1951,52 +1955,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2036,12 +2040,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="59"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2049,7 +2053,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2061,7 +2065,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2237,7 +2241,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2284,7 +2288,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2320,7 +2324,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2330,7 +2334,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2351,10 +2355,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71"/>
+      <c r="R13" s="68"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2368,7 +2372,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2378,7 +2382,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2397,13 +2401,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="72" t="s">
+      <c r="Q14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="73"/>
+      <c r="R14" s="70"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2413,7 +2417,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2423,7 +2427,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="59"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2442,10 +2446,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="73"/>
+      <c r="R15" s="70"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2458,7 +2462,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="59"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2468,7 +2472,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2489,13 +2493,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="63" t="s">
+      <c r="Q16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="64"/>
+      <c r="R16" s="74"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1562</v>
+        <v>1567</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2507,7 +2511,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2519,7 +2523,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="58"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2545,7 +2549,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2555,7 +2559,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="59"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2582,7 +2586,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="58"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2592,7 +2596,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2623,7 +2627,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2633,7 +2637,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2659,7 +2663,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2669,7 +2673,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="59"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2695,7 +2699,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2735,7 +2739,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="58"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2774,7 +2778,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2812,7 +2816,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="58"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2834,9 +2838,15 @@
       <c r="L25" s="3">
         <v>93</v>
       </c>
-      <c r="M25" s="52"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="32"/>
+      <c r="M25" s="52">
+        <v>46225</v>
+      </c>
+      <c r="N25" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="O25" s="32">
+        <v>5</v>
+      </c>
       <c r="Y25"/>
       <c r="AD25"/>
     </row>
@@ -2844,7 +2854,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2854,7 +2864,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2876,7 +2886,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="59"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2886,7 +2896,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="58"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2940,7 +2950,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3080,7 +3090,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3163,7 +3173,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3368,7 +3378,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="60">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3463,7 +3473,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3473,6 +3483,14 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3485,14 +3503,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08551A1-2A14-45C2-80E0-90536F021B4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C5DE03-8B5B-4542-B2D9-8917D37987FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -504,7 +504,7 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>남무호</t>
+    <t>김영택</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1536,6 +1536,30 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1548,21 +1572,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1579,15 +1588,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1955,52 +1955,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
+      <c r="T2" s="69"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
-      <c r="J4" s="71"/>
-      <c r="K4" s="71"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
-      <c r="P4" s="71"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="71"/>
-      <c r="S4" s="71"/>
-      <c r="T4" s="71"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+      <c r="Q4" s="74"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="74"/>
+      <c r="T4" s="74"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2040,12 +2040,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="57" t="s">
+      <c r="Q6" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="59"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="67"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2053,7 +2053,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="60" t="s">
+      <c r="C7" s="68" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2065,7 +2065,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="68">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2241,7 +2241,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="57">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2288,7 +2288,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="64"/>
+      <c r="C12" s="58"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2324,7 +2324,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="64"/>
+      <c r="C13" s="58"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="57">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2355,10 +2355,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="67" t="s">
+      <c r="Q13" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="68"/>
+      <c r="R13" s="71"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2372,7 +2372,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="64"/>
+      <c r="C14" s="58"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2382,7 +2382,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="64"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2401,10 +2401,10 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="69" t="s">
+      <c r="Q14" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="70"/>
+      <c r="R14" s="73"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
         <v>467</v>
@@ -2417,7 +2417,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="64"/>
+      <c r="C15" s="58"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2427,7 +2427,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="65"/>
+      <c r="H15" s="59"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2446,10 +2446,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="69" t="s">
+      <c r="Q15" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="70"/>
+      <c r="R15" s="73"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2462,7 +2462,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="65"/>
+      <c r="C16" s="59"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="63">
+      <c r="H16" s="57">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2493,10 +2493,10 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="Q16" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="74"/>
+      <c r="R16" s="64"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
         <v>1567</v>
@@ -2511,7 +2511,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="63">
+      <c r="C17" s="57">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2523,7 +2523,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="64"/>
+      <c r="H17" s="58"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2549,7 +2549,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="64"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2559,7 +2559,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="65"/>
+      <c r="H18" s="59"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2586,7 +2586,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="64"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2596,7 +2596,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="63">
+      <c r="H19" s="57">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2627,7 +2627,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="64"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2637,7 +2637,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="64"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2663,7 +2663,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="65"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="65"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2699,7 +2699,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="57">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2739,7 +2739,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="58"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2778,7 +2778,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="64"/>
+      <c r="C24" s="58"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2816,7 +2816,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="58"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="64"/>
+      <c r="C26" s="58"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2864,7 +2864,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="63">
+      <c r="H26" s="57">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2886,7 +2886,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2896,7 +2896,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="58"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2950,7 +2950,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="72">
+      <c r="C29" s="60">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3090,7 +3090,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="72">
+      <c r="H33" s="60">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3173,7 +3173,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="72">
+      <c r="C36" s="60">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3378,7 +3378,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="72">
+      <c r="C42" s="60">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3483,14 +3483,6 @@
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3503,6 +3495,14 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kangi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C5DE03-8B5B-4542-B2D9-8917D37987FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DB15E7-87C4-48C2-86FE-0E13B8012BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65989A62-DD22-4017-B1F4-9BE3BB514C20}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="116">
   <si>
     <t>일   자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -505,6 +505,14 @@
   </si>
   <si>
     <t>김영택</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>공성문</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>김경집</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1536,30 +1544,6 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1572,6 +1556,21 @@
     <xf numFmtId="176" fontId="0" fillId="10" borderId="47" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1588,6 +1587,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1955,52 +1963,52 @@
   <sheetData>
     <row r="1" spans="2:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
       <c r="Z2" s="49"/>
     </row>
     <row r="3" spans="2:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:30" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="74"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
     </row>
     <row r="5" spans="2:30" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="2:30" ht="21.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -2040,12 +2048,12 @@
       <c r="O6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="Q6" s="65" t="s">
+      <c r="Q6" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="67"/>
+      <c r="R6" s="58"/>
+      <c r="S6" s="58"/>
+      <c r="T6" s="59"/>
       <c r="Y6"/>
       <c r="AD6"/>
     </row>
@@ -2053,7 +2061,7 @@
       <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="60" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="31" t="s">
@@ -2065,7 +2073,7 @@
       <c r="G7" s="3">
         <v>38</v>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="60">
         <v>46034</v>
       </c>
       <c r="I7" s="31" t="s">
@@ -2241,7 +2249,7 @@
       <c r="B11" s="3">
         <v>5</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="63">
         <v>46023</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -2288,7 +2296,7 @@
       <c r="B12" s="3">
         <v>6</v>
       </c>
-      <c r="C12" s="58"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="34" t="s">
         <v>36</v>
       </c>
@@ -2324,7 +2332,7 @@
       <c r="B13" s="5">
         <v>7</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="34" t="s">
         <v>21</v>
       </c>
@@ -2334,7 +2342,7 @@
       <c r="G13" s="3">
         <v>44</v>
       </c>
-      <c r="H13" s="57">
+      <c r="H13" s="63">
         <v>46035</v>
       </c>
       <c r="I13" s="34" t="s">
@@ -2355,10 +2363,10 @@
       <c r="O13" s="32">
         <v>5</v>
       </c>
-      <c r="Q13" s="70" t="s">
+      <c r="Q13" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="R13" s="71"/>
+      <c r="R13" s="68"/>
       <c r="S13" s="18" t="s">
         <v>14</v>
       </c>
@@ -2372,7 +2380,7 @@
       <c r="B14" s="3">
         <v>8</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="64"/>
       <c r="D14" s="34" t="s">
         <v>22</v>
       </c>
@@ -2382,7 +2390,7 @@
       <c r="G14" s="3">
         <v>45</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="34" t="s">
         <v>61</v>
       </c>
@@ -2401,13 +2409,13 @@
       <c r="O14" s="32">
         <v>5</v>
       </c>
-      <c r="Q14" s="72" t="s">
+      <c r="Q14" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="R14" s="73"/>
+      <c r="R14" s="70"/>
       <c r="S14" s="25">
         <f>E44+J44+O44</f>
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="T14" s="15"/>
       <c r="Y14"/>
@@ -2417,7 +2425,7 @@
       <c r="B15" s="4">
         <v>9</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="34" t="s">
         <v>23</v>
       </c>
@@ -2427,7 +2435,7 @@
       <c r="G15" s="3">
         <v>46</v>
       </c>
-      <c r="H15" s="59"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="34" t="s">
         <v>62</v>
       </c>
@@ -2446,10 +2454,10 @@
       <c r="O15" s="32">
         <v>5</v>
       </c>
-      <c r="Q15" s="72" t="s">
+      <c r="Q15" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="73"/>
+      <c r="R15" s="70"/>
       <c r="S15" s="26">
         <f>S11</f>
         <v>1100</v>
@@ -2462,7 +2470,7 @@
       <c r="B16" s="3">
         <v>10</v>
       </c>
-      <c r="C16" s="59"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="34" t="s">
         <v>24</v>
       </c>
@@ -2472,7 +2480,7 @@
       <c r="G16" s="3">
         <v>47</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="63">
         <v>46036</v>
       </c>
       <c r="I16" s="34" t="s">
@@ -2493,13 +2501,13 @@
       <c r="O16" s="32">
         <v>5</v>
       </c>
-      <c r="Q16" s="63" t="s">
+      <c r="Q16" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="R16" s="64"/>
+      <c r="R16" s="74"/>
       <c r="S16" s="27">
         <f>SUM(S14:S15)</f>
-        <v>1567</v>
+        <v>1577</v>
       </c>
       <c r="T16" s="17" t="s">
         <v>70</v>
@@ -2511,7 +2519,7 @@
       <c r="B17" s="3">
         <v>11</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="63">
         <v>46024</v>
       </c>
       <c r="D17" s="34" t="s">
@@ -2523,7 +2531,7 @@
       <c r="G17" s="3">
         <v>48</v>
       </c>
-      <c r="H17" s="58"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="34" t="s">
         <v>64</v>
       </c>
@@ -2549,7 +2557,7 @@
       <c r="B18" s="3">
         <v>12</v>
       </c>
-      <c r="C18" s="58"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="34" t="s">
         <v>26</v>
       </c>
@@ -2559,7 +2567,7 @@
       <c r="G18" s="3">
         <v>49</v>
       </c>
-      <c r="H18" s="59"/>
+      <c r="H18" s="65"/>
       <c r="I18" s="34" t="s">
         <v>65</v>
       </c>
@@ -2586,7 +2594,7 @@
       <c r="B19" s="3">
         <v>13</v>
       </c>
-      <c r="C19" s="58"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="34" t="s">
         <v>27</v>
       </c>
@@ -2596,7 +2604,7 @@
       <c r="G19" s="3">
         <v>50</v>
       </c>
-      <c r="H19" s="57">
+      <c r="H19" s="63">
         <v>46038</v>
       </c>
       <c r="I19" s="34" t="s">
@@ -2627,7 +2635,7 @@
       <c r="B20" s="3">
         <v>14</v>
       </c>
-      <c r="C20" s="58"/>
+      <c r="C20" s="64"/>
       <c r="D20" s="35" t="s">
         <v>28</v>
       </c>
@@ -2637,7 +2645,7 @@
       <c r="G20" s="3">
         <v>51</v>
       </c>
-      <c r="H20" s="58"/>
+      <c r="H20" s="64"/>
       <c r="I20" s="35" t="s">
         <v>67</v>
       </c>
@@ -2663,7 +2671,7 @@
       <c r="B21" s="3">
         <v>15</v>
       </c>
-      <c r="C21" s="59"/>
+      <c r="C21" s="65"/>
       <c r="D21" s="35" t="s">
         <v>35</v>
       </c>
@@ -2673,7 +2681,7 @@
       <c r="G21" s="3">
         <v>52</v>
       </c>
-      <c r="H21" s="59"/>
+      <c r="H21" s="65"/>
       <c r="I21" s="35" t="s">
         <v>68</v>
       </c>
@@ -2699,7 +2707,7 @@
       <c r="B22" s="3">
         <v>16</v>
       </c>
-      <c r="C22" s="57">
+      <c r="C22" s="63">
         <v>46025</v>
       </c>
       <c r="D22" s="35" t="s">
@@ -2739,7 +2747,7 @@
       <c r="B23" s="3">
         <v>17</v>
       </c>
-      <c r="C23" s="58"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="35" t="s">
         <v>30</v>
       </c>
@@ -2778,7 +2786,7 @@
       <c r="B24" s="3">
         <v>18</v>
       </c>
-      <c r="C24" s="58"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="35" t="s">
         <v>31</v>
       </c>
@@ -2816,7 +2824,7 @@
       <c r="B25" s="3">
         <v>19</v>
       </c>
-      <c r="C25" s="58"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="35" t="s">
         <v>32</v>
       </c>
@@ -2854,7 +2862,7 @@
       <c r="B26" s="3">
         <v>20</v>
       </c>
-      <c r="C26" s="58"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="34" t="s">
         <v>33</v>
       </c>
@@ -2864,7 +2872,7 @@
       <c r="G26" s="3">
         <v>57</v>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="63">
         <v>46056</v>
       </c>
       <c r="I26" s="34" t="s">
@@ -2876,9 +2884,15 @@
       <c r="L26" s="3">
         <v>94</v>
       </c>
-      <c r="M26" s="53"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="32"/>
+      <c r="M26" s="63">
+        <v>46235</v>
+      </c>
+      <c r="N26" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="O26" s="32">
+        <v>5</v>
+      </c>
       <c r="Y26"/>
       <c r="AD26"/>
     </row>
@@ -2886,7 +2900,7 @@
       <c r="B27" s="3">
         <v>21</v>
       </c>
-      <c r="C27" s="59"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="34" t="s">
         <v>34</v>
       </c>
@@ -2896,7 +2910,7 @@
       <c r="G27" s="3">
         <v>58</v>
       </c>
-      <c r="H27" s="58"/>
+      <c r="H27" s="64"/>
       <c r="I27" s="34" t="s">
         <v>76</v>
       </c>
@@ -2906,9 +2920,13 @@
       <c r="L27" s="3">
         <v>95</v>
       </c>
-      <c r="M27" s="53"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="36"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="O27" s="36">
+        <v>5</v>
+      </c>
       <c r="Y27"/>
       <c r="AD27"/>
     </row>
@@ -2950,7 +2968,7 @@
       <c r="B29" s="5">
         <v>23</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="72">
         <v>46027</v>
       </c>
       <c r="D29" s="37" t="s">
@@ -3090,7 +3108,7 @@
       <c r="G33" s="3">
         <v>64</v>
       </c>
-      <c r="H33" s="60">
+      <c r="H33" s="72">
         <v>46073</v>
       </c>
       <c r="I33" s="34" t="s">
@@ -3173,7 +3191,7 @@
       <c r="B36" s="6">
         <v>30</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="72">
         <v>46028</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -3378,7 +3396,7 @@
       <c r="B42" s="3">
         <v>36</v>
       </c>
-      <c r="C42" s="60">
+      <c r="C42" s="72">
         <v>46029</v>
       </c>
       <c r="D42" s="35" t="s">
@@ -3473,7 +3491,7 @@
       <c r="N44" s="39"/>
       <c r="O44" s="40">
         <f>SUM(O7:O43)</f>
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="P44" s="2"/>
       <c r="U44" s="2"/>
@@ -3482,7 +3500,16 @@
     </row>
     <row r="45" spans="2:30" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
+    <mergeCell ref="C22:C27"/>
+    <mergeCell ref="C29:C35"/>
+    <mergeCell ref="C36:C41"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="M26:M27"/>
     <mergeCell ref="Q6:T6"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="C11:C16"/>
@@ -3495,14 +3522,6 @@
     <mergeCell ref="H13:H15"/>
     <mergeCell ref="H16:H18"/>
     <mergeCell ref="B4:T4"/>
-    <mergeCell ref="C22:C27"/>
-    <mergeCell ref="C29:C35"/>
-    <mergeCell ref="C36:C41"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="H33:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
